--- a/research/traditional_assets/database/data/morocco/morocco_real_estate_operations_services.xlsx
+++ b/research/traditional_assets/database/data/morocco/morocco_real_estate_operations_services.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08819753500210611</v>
+        <v>0.08794590289009938</v>
       </c>
       <c r="C2">
-        <v>882.8848045667299</v>
+        <v>878.4381232188824</v>
       </c>
       <c r="D2">
-        <v>826.7848045667299</v>
+        <v>831.7211232188824</v>
       </c>
       <c r="E2">
-        <v>-343.1</v>
+        <v>-333.717</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>9.383000000000001</v>
       </c>
       <c r="G2">
         <v>56.1</v>
@@ -1579,28 +1579,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.4719649</v>
       </c>
       <c r="N2">
-        <v>54.90499999999999</v>
+        <v>54.43303509999999</v>
       </c>
       <c r="O2">
-        <v>17.5696</v>
+        <v>17.418571232</v>
       </c>
       <c r="P2">
-        <v>37.33539999999999</v>
+        <v>37.01446386799999</v>
       </c>
       <c r="Q2">
-        <v>37.80539999999999</v>
+        <v>37.48446386799999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08819753500210611</v>
+        <v>0.08848875039403978</v>
       </c>
       <c r="T2">
-        <v>0.5525820103960151</v>
+        <v>0.5563775231946948</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>116.3328035622988</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08794590289009938</v>
+        <v>0.08769427077809264</v>
       </c>
       <c r="C3">
-        <v>878.4381232188824</v>
+        <v>874.0507404942075</v>
       </c>
       <c r="D3">
-        <v>831.7211232188824</v>
+        <v>836.7167404942074</v>
       </c>
       <c r="E3">
-        <v>-333.717</v>
+        <v>-324.334</v>
       </c>
       <c r="F3">
-        <v>9.383000000000001</v>
+        <v>18.766</v>
       </c>
       <c r="G3">
         <v>56.1</v>
@@ -1661,28 +1661,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M3">
-        <v>0.4719649</v>
+        <v>0.9439298</v>
       </c>
       <c r="N3">
-        <v>54.43303509999999</v>
+        <v>53.96107019999999</v>
       </c>
       <c r="O3">
-        <v>17.418571232</v>
+        <v>17.267542464</v>
       </c>
       <c r="P3">
-        <v>37.01446386799999</v>
+        <v>36.69352773599999</v>
       </c>
       <c r="Q3">
-        <v>37.48446386799999</v>
+        <v>37.16352773599999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08848875039403978</v>
+        <v>0.08878590895723738</v>
       </c>
       <c r="T3">
-        <v>0.5563775231946948</v>
+        <v>0.5602504954382455</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>116.3328035622988</v>
+        <v>58.1664017811494</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08769427077809264</v>
+        <v>0.08744263866608591</v>
       </c>
       <c r="C4">
-        <v>874.0507404942075</v>
+        <v>869.7237313561268</v>
       </c>
       <c r="D4">
-        <v>836.7167404942074</v>
+        <v>841.7727313561268</v>
       </c>
       <c r="E4">
-        <v>-324.334</v>
+        <v>-314.951</v>
       </c>
       <c r="F4">
-        <v>18.766</v>
+        <v>28.149</v>
       </c>
       <c r="G4">
         <v>56.1</v>
@@ -1743,28 +1743,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M4">
-        <v>0.9439298</v>
+        <v>1.4158947</v>
       </c>
       <c r="N4">
-        <v>53.96107019999999</v>
+        <v>53.48910529999999</v>
       </c>
       <c r="O4">
-        <v>17.267542464</v>
+        <v>17.116513696</v>
       </c>
       <c r="P4">
-        <v>36.69352773599999</v>
+        <v>36.37259160399999</v>
       </c>
       <c r="Q4">
-        <v>37.16352773599999</v>
+        <v>36.84259160399999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08878590895723738</v>
+        <v>0.08908919450111949</v>
       </c>
       <c r="T4">
-        <v>0.5602504954382455</v>
+        <v>0.5642033227796014</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>58.1664017811494</v>
+        <v>38.77760118743293</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08744263866608591</v>
+        <v>0.08719100655407915</v>
       </c>
       <c r="C5">
-        <v>869.7237313561268</v>
+        <v>865.4581969085554</v>
       </c>
       <c r="D5">
-        <v>841.7727313561268</v>
+        <v>846.8901969085554</v>
       </c>
       <c r="E5">
-        <v>-314.951</v>
+        <v>-305.568</v>
       </c>
       <c r="F5">
-        <v>28.149</v>
+        <v>37.532</v>
       </c>
       <c r="G5">
         <v>56.1</v>
@@ -1825,28 +1825,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M5">
-        <v>1.4158947</v>
+        <v>1.8878596</v>
       </c>
       <c r="N5">
-        <v>53.48910529999999</v>
+        <v>53.0171404</v>
       </c>
       <c r="O5">
-        <v>17.116513696</v>
+        <v>16.965484928</v>
       </c>
       <c r="P5">
-        <v>36.37259160399999</v>
+        <v>36.05165547199999</v>
       </c>
       <c r="Q5">
-        <v>36.84259160399999</v>
+        <v>36.52165547199999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08908919450111949</v>
+        <v>0.08939879849383245</v>
       </c>
       <c r="T5">
-        <v>0.5642033227796014</v>
+        <v>0.5682385006905688</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>38.77760118743293</v>
+        <v>29.0832008905747</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08719100655407915</v>
+        <v>0.08693937444207242</v>
       </c>
       <c r="C6">
-        <v>865.4581969085554</v>
+        <v>861.2552651953487</v>
       </c>
       <c r="D6">
-        <v>846.8901969085554</v>
+        <v>852.0702651953486</v>
       </c>
       <c r="E6">
-        <v>-305.568</v>
+        <v>-296.185</v>
       </c>
       <c r="F6">
-        <v>37.532</v>
+        <v>46.91500000000001</v>
       </c>
       <c r="G6">
         <v>56.1</v>
@@ -1907,28 +1907,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M6">
-        <v>1.8878596</v>
+        <v>2.3598245</v>
       </c>
       <c r="N6">
-        <v>53.0171404</v>
+        <v>52.54517549999999</v>
       </c>
       <c r="O6">
-        <v>16.965484928</v>
+        <v>16.81445616</v>
       </c>
       <c r="P6">
-        <v>36.05165547199999</v>
+        <v>35.73071933999999</v>
       </c>
       <c r="Q6">
-        <v>36.52165547199999</v>
+        <v>36.20071933999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08939879849383245</v>
+        <v>0.0897149204653394</v>
       </c>
       <c r="T6">
-        <v>0.5682385006905688</v>
+        <v>0.5723586297154515</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>29.0832008905747</v>
+        <v>23.26656071245976</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08693937444207242</v>
+        <v>0.08668774233006568</v>
       </c>
       <c r="C7">
-        <v>861.2552651953487</v>
+        <v>857.1160920292795</v>
       </c>
       <c r="D7">
-        <v>852.0702651953486</v>
+        <v>857.3140920292794</v>
       </c>
       <c r="E7">
-        <v>-296.185</v>
+        <v>-286.802</v>
       </c>
       <c r="F7">
-        <v>46.91500000000001</v>
+        <v>56.29800000000001</v>
       </c>
       <c r="G7">
         <v>56.1</v>
@@ -1989,28 +1989,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M7">
-        <v>2.3598245</v>
+        <v>2.8317894</v>
       </c>
       <c r="N7">
-        <v>52.54517549999999</v>
+        <v>52.0732106</v>
       </c>
       <c r="O7">
-        <v>16.81445616</v>
+        <v>16.663427392</v>
       </c>
       <c r="P7">
-        <v>35.73071933999999</v>
+        <v>35.40978320799999</v>
       </c>
       <c r="Q7">
-        <v>36.20071933999999</v>
+        <v>35.87978320799999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0897149204653394</v>
+        <v>0.09003776843624009</v>
       </c>
       <c r="T7">
-        <v>0.5723586297154515</v>
+        <v>0.5765664210600123</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>23.26656071245976</v>
+        <v>19.38880059371646</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08668774233006568</v>
+        <v>0.08643611021805894</v>
       </c>
       <c r="C8">
-        <v>857.1160920292795</v>
+        <v>853.0418618518054</v>
       </c>
       <c r="D8">
-        <v>857.3140920292794</v>
+        <v>862.6228618518054</v>
       </c>
       <c r="E8">
-        <v>-286.802</v>
+        <v>-277.419</v>
       </c>
       <c r="F8">
-        <v>56.298</v>
+        <v>65.681</v>
       </c>
       <c r="G8">
         <v>56.1</v>
@@ -2071,28 +2071,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M8">
-        <v>2.8317894</v>
+        <v>3.3037543</v>
       </c>
       <c r="N8">
-        <v>52.0732106</v>
+        <v>51.60124569999999</v>
       </c>
       <c r="O8">
-        <v>16.663427392</v>
+        <v>16.512398624</v>
       </c>
       <c r="P8">
-        <v>35.40978320799999</v>
+        <v>35.08884707599999</v>
       </c>
       <c r="Q8">
-        <v>35.87978320799999</v>
+        <v>35.55884707599999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09003776843624009</v>
+        <v>0.09036755937425692</v>
       </c>
       <c r="T8">
-        <v>0.5765664210600123</v>
+        <v>0.5808647025410154</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.38880059371647</v>
+        <v>16.61897193747126</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08643611021805893</v>
+        <v>0.08618447810605222</v>
       </c>
       <c r="C9">
-        <v>853.0418618518057</v>
+        <v>849.0337886249837</v>
       </c>
       <c r="D9">
-        <v>862.6228618518057</v>
+        <v>867.9977886249836</v>
       </c>
       <c r="E9">
-        <v>-277.419</v>
+        <v>-268.036</v>
       </c>
       <c r="F9">
-        <v>65.68100000000001</v>
+        <v>75.06400000000001</v>
       </c>
       <c r="G9">
         <v>56.1</v>
@@ -2153,28 +2153,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M9">
-        <v>3.3037543</v>
+        <v>3.7757192</v>
       </c>
       <c r="N9">
-        <v>51.60124569999999</v>
+        <v>51.1292808</v>
       </c>
       <c r="O9">
-        <v>16.512398624</v>
+        <v>16.361369856</v>
       </c>
       <c r="P9">
-        <v>35.08884707599999</v>
+        <v>34.76791094399999</v>
       </c>
       <c r="Q9">
-        <v>35.55884707599999</v>
+        <v>35.23791094399999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09036755937425692</v>
+        <v>0.09070451968049154</v>
       </c>
       <c r="T9">
-        <v>0.5808647025410154</v>
+        <v>0.5852564249237795</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>16.61897193747125</v>
+        <v>14.54160044528735</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08618447810605222</v>
+        <v>0.08593284599404546</v>
       </c>
       <c r="C10">
-        <v>849.0337886249837</v>
+        <v>845.0931167569408</v>
       </c>
       <c r="D10">
-        <v>867.9977886249836</v>
+        <v>873.4401167569408</v>
       </c>
       <c r="E10">
-        <v>-268.036</v>
+        <v>-258.653</v>
       </c>
       <c r="F10">
-        <v>75.06400000000001</v>
+        <v>84.447</v>
       </c>
       <c r="G10">
         <v>56.1</v>
@@ -2235,28 +2235,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M10">
-        <v>3.7757192</v>
+        <v>4.2476841</v>
       </c>
       <c r="N10">
-        <v>51.1292808</v>
+        <v>50.65731589999999</v>
       </c>
       <c r="O10">
-        <v>16.361369856</v>
+        <v>16.210341088</v>
       </c>
       <c r="P10">
-        <v>34.76791094399999</v>
+        <v>34.44697481199999</v>
       </c>
       <c r="Q10">
-        <v>35.23791094399999</v>
+        <v>34.91697481199999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09070451968049154</v>
+        <v>0.09104888570774226</v>
       </c>
       <c r="T10">
-        <v>0.5852564249237795</v>
+        <v>0.5897446686775932</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.54160044528735</v>
+        <v>12.92586706247764</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08593284599404546</v>
+        <v>0.08578321388203872</v>
       </c>
       <c r="C11">
-        <v>845.0931167569408</v>
+        <v>838.9788557274334</v>
       </c>
       <c r="D11">
-        <v>873.4401167569408</v>
+        <v>876.7088557274334</v>
       </c>
       <c r="E11">
-        <v>-258.653</v>
+        <v>-249.27</v>
       </c>
       <c r="F11">
-        <v>84.447</v>
+        <v>93.83</v>
       </c>
       <c r="G11">
         <v>56.1</v>
@@ -2317,45 +2317,45 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M11">
-        <v>4.2476841</v>
+        <v>4.860393999999999</v>
       </c>
       <c r="N11">
-        <v>50.65731589999999</v>
+        <v>50.04460599999999</v>
       </c>
       <c r="O11">
-        <v>16.210341088</v>
+        <v>16.01427392</v>
       </c>
       <c r="P11">
-        <v>34.44697481199999</v>
+        <v>34.03033207999999</v>
       </c>
       <c r="Q11">
-        <v>34.91697481199999</v>
+        <v>34.50033207999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09104888570774226</v>
+        <v>0.09140090431337636</v>
       </c>
       <c r="T11">
-        <v>0.5897446686775932</v>
+        <v>0.5943326511814918</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.32</v>
       </c>
       <c r="W11">
-        <v>0.034204</v>
+        <v>0.035224</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>12.92586706247764</v>
+        <v>11.2964093034433</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08578321388203872</v>
+        <v>0.08554178177003198</v>
       </c>
       <c r="C12">
-        <v>838.9788557274334</v>
+        <v>834.9218794039284</v>
       </c>
       <c r="D12">
-        <v>876.7088557274334</v>
+        <v>882.0348794039284</v>
       </c>
       <c r="E12">
-        <v>-249.27</v>
+        <v>-239.887</v>
       </c>
       <c r="F12">
-        <v>93.83000000000001</v>
+        <v>103.213</v>
       </c>
       <c r="G12">
         <v>56.1</v>
@@ -2399,28 +2399,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M12">
-        <v>4.860394</v>
+        <v>5.3464334</v>
       </c>
       <c r="N12">
-        <v>50.04460599999999</v>
+        <v>49.55856659999999</v>
       </c>
       <c r="O12">
-        <v>16.01427392</v>
+        <v>15.858741312</v>
       </c>
       <c r="P12">
-        <v>34.03033207999999</v>
+        <v>33.69982528799999</v>
       </c>
       <c r="Q12">
-        <v>34.50033207999999</v>
+        <v>34.16982528799999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09140090431337636</v>
+        <v>0.09176083344947414</v>
       </c>
       <c r="T12">
-        <v>0.5943326511814918</v>
+        <v>0.5990237344158149</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.2964093034433</v>
+        <v>10.26946300313027</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08554178177003198</v>
+        <v>0.08543906965802524</v>
       </c>
       <c r="C13">
-        <v>834.9218794039284</v>
+        <v>827.8243938246445</v>
       </c>
       <c r="D13">
-        <v>882.0348794039284</v>
+        <v>884.3203938246445</v>
       </c>
       <c r="E13">
-        <v>-239.887</v>
+        <v>-230.504</v>
       </c>
       <c r="F13">
-        <v>103.213</v>
+        <v>112.596</v>
       </c>
       <c r="G13">
         <v>56.1</v>
@@ -2481,45 +2481,45 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M13">
-        <v>5.3464334</v>
+        <v>6.023886</v>
       </c>
       <c r="N13">
-        <v>49.55856659999999</v>
+        <v>48.881114</v>
       </c>
       <c r="O13">
-        <v>15.858741312</v>
+        <v>15.64195648</v>
       </c>
       <c r="P13">
-        <v>33.69982528799999</v>
+        <v>33.23915752</v>
       </c>
       <c r="Q13">
-        <v>34.16982528799999</v>
+        <v>33.70915752</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09176083344947414</v>
+        <v>0.0921289427932105</v>
       </c>
       <c r="T13">
-        <v>0.5990237344158149</v>
+        <v>0.603821433178191</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.32</v>
       </c>
       <c r="W13">
-        <v>0.035224</v>
+        <v>0.03638</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>10.26946300313027</v>
+        <v>9.114548316485404</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08543906965802524</v>
+        <v>0.08520919754601849</v>
       </c>
       <c r="C14">
-        <v>827.8243938246445</v>
+        <v>823.5995956982487</v>
       </c>
       <c r="D14">
-        <v>884.3203938246445</v>
+        <v>889.4785956982487</v>
       </c>
       <c r="E14">
-        <v>-230.504</v>
+        <v>-221.121</v>
       </c>
       <c r="F14">
-        <v>112.596</v>
+        <v>121.979</v>
       </c>
       <c r="G14">
         <v>56.1</v>
@@ -2563,28 +2563,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M14">
-        <v>6.023886</v>
+        <v>6.525876500000001</v>
       </c>
       <c r="N14">
-        <v>48.881114</v>
+        <v>48.37912349999999</v>
       </c>
       <c r="O14">
-        <v>15.64195648</v>
+        <v>15.48131952</v>
       </c>
       <c r="P14">
-        <v>33.23915752</v>
+        <v>32.89780397999999</v>
       </c>
       <c r="Q14">
-        <v>33.70915752</v>
+        <v>33.36780397999999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0921289427932105</v>
+        <v>0.09250551442071092</v>
       </c>
       <c r="T14">
-        <v>0.603821433178191</v>
+        <v>0.6087294238661389</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.114548316485404</v>
+        <v>8.413429215217295</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08520919754601849</v>
+        <v>0.08497932543401177</v>
       </c>
       <c r="C15">
-        <v>823.5995956982487</v>
+        <v>819.4353257583746</v>
       </c>
       <c r="D15">
-        <v>889.4785956982487</v>
+        <v>894.6973257583746</v>
       </c>
       <c r="E15">
-        <v>-221.121</v>
+        <v>-211.738</v>
       </c>
       <c r="F15">
-        <v>121.979</v>
+        <v>131.362</v>
       </c>
       <c r="G15">
         <v>56.1</v>
@@ -2645,28 +2645,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M15">
-        <v>6.525876500000001</v>
+        <v>7.027867000000001</v>
       </c>
       <c r="N15">
-        <v>48.37912349999999</v>
+        <v>47.87713299999999</v>
       </c>
       <c r="O15">
-        <v>15.48131952</v>
+        <v>15.32068256</v>
       </c>
       <c r="P15">
-        <v>32.89780397999999</v>
+        <v>32.55645043999999</v>
       </c>
       <c r="Q15">
-        <v>33.36780397999999</v>
+        <v>33.02645043999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09250551442071092</v>
+        <v>0.09289084352792065</v>
       </c>
       <c r="T15">
-        <v>0.6087294238661389</v>
+        <v>0.6137515538724111</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.413429215217295</v>
+        <v>7.812469985558916</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08497932543401177</v>
+        <v>0.08483105332200502</v>
       </c>
       <c r="C16">
-        <v>819.4353257583746</v>
+        <v>813.4511236591779</v>
       </c>
       <c r="D16">
-        <v>894.6973257583746</v>
+        <v>898.0961236591779</v>
       </c>
       <c r="E16">
-        <v>-211.738</v>
+        <v>-202.355</v>
       </c>
       <c r="F16">
-        <v>131.362</v>
+        <v>140.745</v>
       </c>
       <c r="G16">
         <v>56.1</v>
@@ -2727,45 +2727,45 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M16">
-        <v>7.027867000000001</v>
+        <v>7.642453500000002</v>
       </c>
       <c r="N16">
-        <v>47.87713299999999</v>
+        <v>47.26254649999999</v>
       </c>
       <c r="O16">
-        <v>15.32068256</v>
+        <v>15.12401488</v>
       </c>
       <c r="P16">
-        <v>32.55645043999999</v>
+        <v>32.13853161999999</v>
       </c>
       <c r="Q16">
-        <v>33.02645043999999</v>
+        <v>32.60853161999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09289084352792065</v>
+        <v>0.09328523920235884</v>
       </c>
       <c r="T16">
-        <v>0.6137515538724111</v>
+        <v>0.6188918516435369</v>
       </c>
       <c r="U16">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V16">
         <v>0.32</v>
       </c>
       <c r="W16">
-        <v>0.03638</v>
+        <v>0.036924</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y16">
-        <v>7.812469985558916</v>
+        <v>7.184211196051108</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08483105332200502</v>
+        <v>0.08460662120999828</v>
       </c>
       <c r="C17">
-        <v>813.4511236591779</v>
+        <v>809.2621241553092</v>
       </c>
       <c r="D17">
-        <v>898.0961236591779</v>
+        <v>903.2901241553092</v>
       </c>
       <c r="E17">
-        <v>-202.355</v>
+        <v>-192.972</v>
       </c>
       <c r="F17">
-        <v>140.745</v>
+        <v>150.128</v>
       </c>
       <c r="G17">
         <v>56.1</v>
@@ -2809,28 +2809,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M17">
-        <v>7.6424535</v>
+        <v>8.1519504</v>
       </c>
       <c r="N17">
-        <v>47.26254649999999</v>
+        <v>46.7530496</v>
       </c>
       <c r="O17">
-        <v>15.12401488</v>
+        <v>14.960975872</v>
       </c>
       <c r="P17">
-        <v>32.13853161999999</v>
+        <v>31.792073728</v>
       </c>
       <c r="Q17">
-        <v>32.60853161999999</v>
+        <v>32.262073728</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09328523920235884</v>
+        <v>0.09368902524999795</v>
       </c>
       <c r="T17">
-        <v>0.6188918516435369</v>
+        <v>0.6241545374568322</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.18421119605111</v>
+        <v>6.735197996297916</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08460662120999828</v>
+        <v>0.08438218909799154</v>
       </c>
       <c r="C18">
-        <v>809.2621241553092</v>
+        <v>805.133551523443</v>
       </c>
       <c r="D18">
-        <v>903.2901241553092</v>
+        <v>908.544551523443</v>
       </c>
       <c r="E18">
-        <v>-192.972</v>
+        <v>-183.589</v>
       </c>
       <c r="F18">
-        <v>150.128</v>
+        <v>159.511</v>
       </c>
       <c r="G18">
         <v>56.1</v>
@@ -2891,28 +2891,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M18">
-        <v>8.1519504</v>
+        <v>8.661447300000001</v>
       </c>
       <c r="N18">
-        <v>46.7530496</v>
+        <v>46.2435527</v>
       </c>
       <c r="O18">
-        <v>14.960975872</v>
+        <v>14.797936864</v>
       </c>
       <c r="P18">
-        <v>31.792073728</v>
+        <v>31.44561583599999</v>
       </c>
       <c r="Q18">
-        <v>32.262073728</v>
+        <v>31.91561583599999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09368902524999795</v>
+        <v>0.09410254108191753</v>
       </c>
       <c r="T18">
-        <v>0.6241545374568322</v>
+        <v>0.6295440349764722</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.735197996297916</v>
+        <v>6.339009878868627</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08438218909799154</v>
+        <v>0.0842801569859848</v>
       </c>
       <c r="C19">
-        <v>805.133551523443</v>
+        <v>798.1596040509032</v>
       </c>
       <c r="D19">
-        <v>908.544551523443</v>
+        <v>910.9536040509032</v>
       </c>
       <c r="E19">
-        <v>-183.589</v>
+        <v>-174.206</v>
       </c>
       <c r="F19">
-        <v>159.511</v>
+        <v>168.894</v>
       </c>
       <c r="G19">
         <v>56.1</v>
@@ -2973,45 +2973,45 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M19">
-        <v>8.661447300000001</v>
+        <v>9.339838200000003</v>
       </c>
       <c r="N19">
-        <v>46.2435527</v>
+        <v>45.56516179999999</v>
       </c>
       <c r="O19">
-        <v>14.797936864</v>
+        <v>14.580851776</v>
       </c>
       <c r="P19">
-        <v>31.44561583599999</v>
+        <v>30.984310024</v>
       </c>
       <c r="Q19">
-        <v>31.91561583599999</v>
+        <v>31.45431002399999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09410254108191753</v>
+        <v>0.09452614266583512</v>
       </c>
       <c r="T19">
-        <v>0.6295440349764722</v>
+        <v>0.6350649836551275</v>
       </c>
       <c r="U19">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V19">
         <v>0.32</v>
       </c>
       <c r="W19">
-        <v>0.036924</v>
+        <v>0.037604</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y19">
-        <v>6.339009878868627</v>
+        <v>5.878581494056286</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0842801569859848</v>
+        <v>0.08406252487397807</v>
       </c>
       <c r="C20">
-        <v>798.1596040509032</v>
+        <v>793.9579860282481</v>
       </c>
       <c r="D20">
-        <v>910.9536040509032</v>
+        <v>916.1349860282481</v>
       </c>
       <c r="E20">
-        <v>-174.206</v>
+        <v>-164.823</v>
       </c>
       <c r="F20">
-        <v>168.894</v>
+        <v>178.277</v>
       </c>
       <c r="G20">
         <v>56.1</v>
@@ -3055,28 +3055,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M20">
-        <v>9.339838200000001</v>
+        <v>9.858718100000001</v>
       </c>
       <c r="N20">
-        <v>45.56516179999999</v>
+        <v>45.0462819</v>
       </c>
       <c r="O20">
-        <v>14.580851776</v>
+        <v>14.414810208</v>
       </c>
       <c r="P20">
-        <v>30.984310024</v>
+        <v>30.631471692</v>
       </c>
       <c r="Q20">
-        <v>31.45431002399999</v>
+        <v>31.101471692</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09452614266583512</v>
+        <v>0.09496020354812107</v>
       </c>
       <c r="T20">
-        <v>0.6350649836551275</v>
+        <v>0.6407222520542436</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.878581494056288</v>
+        <v>5.569182468053326</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08406252487397807</v>
+        <v>0.08384489276197132</v>
       </c>
       <c r="C21">
-        <v>793.9579860282481</v>
+        <v>789.8156471897878</v>
       </c>
       <c r="D21">
-        <v>916.1349860282481</v>
+        <v>921.3756471897877</v>
       </c>
       <c r="E21">
-        <v>-164.823</v>
+        <v>-155.44</v>
       </c>
       <c r="F21">
-        <v>178.277</v>
+        <v>187.66</v>
       </c>
       <c r="G21">
         <v>56.1</v>
@@ -3137,28 +3137,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M21">
-        <v>9.858718100000001</v>
+        <v>10.377598</v>
       </c>
       <c r="N21">
-        <v>45.0462819</v>
+        <v>44.527402</v>
       </c>
       <c r="O21">
-        <v>14.414810208</v>
+        <v>14.24876864</v>
       </c>
       <c r="P21">
-        <v>30.631471692</v>
+        <v>30.27863336</v>
       </c>
       <c r="Q21">
-        <v>31.101471692</v>
+        <v>30.74863336</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09496020354812107</v>
+        <v>0.09540511595246415</v>
       </c>
       <c r="T21">
-        <v>0.6407222520542436</v>
+        <v>0.6465209521633376</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.569182468053326</v>
+        <v>5.290723344650658</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08384489276197132</v>
+        <v>0.08362726064996459</v>
       </c>
       <c r="C22">
-        <v>789.8156471897878</v>
+        <v>785.7336106908195</v>
       </c>
       <c r="D22">
-        <v>921.3756471897877</v>
+        <v>926.6766106908195</v>
       </c>
       <c r="E22">
-        <v>-155.44</v>
+        <v>-146.057</v>
       </c>
       <c r="F22">
-        <v>187.66</v>
+        <v>197.043</v>
       </c>
       <c r="G22">
         <v>56.1</v>
@@ -3219,28 +3219,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M22">
-        <v>10.377598</v>
+        <v>10.8964779</v>
       </c>
       <c r="N22">
-        <v>44.527402</v>
+        <v>44.00852209999999</v>
       </c>
       <c r="O22">
-        <v>14.24876864</v>
+        <v>14.082727072</v>
       </c>
       <c r="P22">
-        <v>30.27863336</v>
+        <v>29.925795028</v>
       </c>
       <c r="Q22">
-        <v>30.74863336</v>
+        <v>30.39579502799999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09540511595246415</v>
+        <v>0.09586129196198048</v>
       </c>
       <c r="T22">
-        <v>0.6465209521633376</v>
+        <v>0.6524664548068391</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.290723344650658</v>
+        <v>5.038784137762532</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08362726064996459</v>
+        <v>0.08340962853795784</v>
       </c>
       <c r="C23">
-        <v>785.7336106908195</v>
+        <v>781.7129233690305</v>
       </c>
       <c r="D23">
-        <v>926.6766106908195</v>
+        <v>932.0389233690305</v>
       </c>
       <c r="E23">
-        <v>-146.057</v>
+        <v>-136.674</v>
       </c>
       <c r="F23">
-        <v>197.043</v>
+        <v>206.426</v>
       </c>
       <c r="G23">
         <v>56.1</v>
@@ -3301,28 +3301,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M23">
-        <v>10.8964779</v>
+        <v>11.4153578</v>
       </c>
       <c r="N23">
-        <v>44.00852209999999</v>
+        <v>43.48964219999999</v>
       </c>
       <c r="O23">
-        <v>14.082727072</v>
+        <v>13.916685504</v>
       </c>
       <c r="P23">
-        <v>29.925795028</v>
+        <v>29.57295669599999</v>
       </c>
       <c r="Q23">
-        <v>30.39579502799999</v>
+        <v>30.04295669599999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09586129196198048</v>
+        <v>0.09632916479225365</v>
       </c>
       <c r="T23">
-        <v>0.6524664548068391</v>
+        <v>0.6585644062360714</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.038784137762533</v>
+        <v>4.809748495136963</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08340962853795784</v>
+        <v>0.08319199642595111</v>
       </c>
       <c r="C24">
-        <v>781.7129233690305</v>
+        <v>777.7546564336844</v>
       </c>
       <c r="D24">
-        <v>932.0389233690305</v>
+        <v>937.4636564336845</v>
       </c>
       <c r="E24">
-        <v>-136.674</v>
+        <v>-127.291</v>
       </c>
       <c r="F24">
-        <v>206.426</v>
+        <v>215.809</v>
       </c>
       <c r="G24">
         <v>56.1</v>
@@ -3383,28 +3383,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M24">
-        <v>11.4153578</v>
+        <v>11.9342377</v>
       </c>
       <c r="N24">
-        <v>43.48964219999999</v>
+        <v>42.97076229999999</v>
       </c>
       <c r="O24">
-        <v>13.916685504</v>
+        <v>13.750643936</v>
       </c>
       <c r="P24">
-        <v>29.57295669599999</v>
+        <v>29.22011836399999</v>
       </c>
       <c r="Q24">
-        <v>30.04295669599999</v>
+        <v>29.69011836399999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09632916479225365</v>
+        <v>0.09680919016357287</v>
       </c>
       <c r="T24">
-        <v>0.6585644062360714</v>
+        <v>0.6648207460141147</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.809748495136963</v>
+        <v>4.600628995348398</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08319199642595111</v>
+        <v>0.08338236431394437</v>
       </c>
       <c r="C25">
-        <v>777.7546564336844</v>
+        <v>763.6230734319627</v>
       </c>
       <c r="D25">
-        <v>937.4636564336845</v>
+        <v>932.7150734319627</v>
       </c>
       <c r="E25">
-        <v>-127.291</v>
+        <v>-117.908</v>
       </c>
       <c r="F25">
-        <v>215.809</v>
+        <v>225.192</v>
       </c>
       <c r="G25">
         <v>56.1</v>
@@ -3465,45 +3465,45 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M25">
-        <v>11.9342377</v>
+        <v>13.0160976</v>
       </c>
       <c r="N25">
-        <v>42.97076229999999</v>
+        <v>41.88890239999999</v>
       </c>
       <c r="O25">
-        <v>13.750643936</v>
+        <v>13.404448768</v>
       </c>
       <c r="P25">
-        <v>29.22011836399999</v>
+        <v>28.48445363199999</v>
       </c>
       <c r="Q25">
-        <v>29.69011836399999</v>
+        <v>28.95445363199999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09680919016357287</v>
+        <v>0.09730184778150575</v>
       </c>
       <c r="T25">
-        <v>0.6648207460141147</v>
+        <v>0.671241726312633</v>
       </c>
       <c r="U25">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V25">
         <v>0.32</v>
       </c>
       <c r="W25">
-        <v>0.037604</v>
+        <v>0.039304</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>4.600628995348398</v>
+        <v>4.218238191453019</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08338236431394437</v>
+        <v>0.08318173220193763</v>
       </c>
       <c r="C26">
-        <v>763.6230734319627</v>
+        <v>759.2460639000416</v>
       </c>
       <c r="D26">
-        <v>932.7150734319627</v>
+        <v>937.7210639000416</v>
       </c>
       <c r="E26">
-        <v>-117.908</v>
+        <v>-108.525</v>
       </c>
       <c r="F26">
-        <v>225.192</v>
+        <v>234.575</v>
       </c>
       <c r="G26">
         <v>56.1</v>
@@ -3547,28 +3547,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M26">
-        <v>13.0160976</v>
+        <v>13.558435</v>
       </c>
       <c r="N26">
-        <v>41.88890239999999</v>
+        <v>41.34656499999999</v>
       </c>
       <c r="O26">
-        <v>13.404448768</v>
+        <v>13.2309008</v>
       </c>
       <c r="P26">
-        <v>28.48445363199999</v>
+        <v>28.11566419999999</v>
       </c>
       <c r="Q26">
-        <v>28.95445363199999</v>
+        <v>28.58566419999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09730184778150575</v>
+        <v>0.09780764293591683</v>
       </c>
       <c r="T26">
-        <v>0.671241726312633</v>
+        <v>0.6778339327524451</v>
       </c>
       <c r="U26">
         <v>0.0578</v>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.218238191453019</v>
+        <v>4.049508663794899</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08318173220193763</v>
+        <v>0.08359990008993089</v>
       </c>
       <c r="C27">
-        <v>759.2460639000416</v>
+        <v>739.4893635493804</v>
       </c>
       <c r="D27">
-        <v>937.7210639000416</v>
+        <v>927.3473635493804</v>
       </c>
       <c r="E27">
-        <v>-108.525</v>
+        <v>-99.142</v>
       </c>
       <c r="F27">
-        <v>234.575</v>
+        <v>243.958</v>
       </c>
       <c r="G27">
         <v>56.1</v>
@@ -3629,45 +3629,45 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M27">
-        <v>13.558435</v>
+        <v>14.9546254</v>
       </c>
       <c r="N27">
-        <v>41.34656499999999</v>
+        <v>39.95037459999999</v>
       </c>
       <c r="O27">
-        <v>13.2309008</v>
+        <v>12.784119872</v>
       </c>
       <c r="P27">
-        <v>28.11566419999999</v>
+        <v>27.16625472799999</v>
       </c>
       <c r="Q27">
-        <v>28.58566419999999</v>
+        <v>27.63625472799999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09780764293591683</v>
+        <v>0.09832710822963633</v>
       </c>
       <c r="T27">
-        <v>0.6778339327524451</v>
+        <v>0.6846043069338738</v>
       </c>
       <c r="U27">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V27">
         <v>0.32</v>
       </c>
       <c r="W27">
-        <v>0.039304</v>
+        <v>0.041684</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>4.049508663794899</v>
+        <v>3.671439339430059</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08359990008993089</v>
+        <v>0.08342306797792415</v>
       </c>
       <c r="C28">
-        <v>739.4893635493804</v>
+        <v>734.4649871724336</v>
       </c>
       <c r="D28">
-        <v>927.3473635493804</v>
+        <v>931.7059871724335</v>
       </c>
       <c r="E28">
-        <v>-99.142</v>
+        <v>-89.75899999999999</v>
       </c>
       <c r="F28">
-        <v>243.958</v>
+        <v>253.341</v>
       </c>
       <c r="G28">
         <v>56.1</v>
@@ -3711,28 +3711,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M28">
-        <v>14.9546254</v>
+        <v>15.5298033</v>
       </c>
       <c r="N28">
-        <v>39.95037459999999</v>
+        <v>39.37519669999999</v>
       </c>
       <c r="O28">
-        <v>12.784119872</v>
+        <v>12.600062944</v>
       </c>
       <c r="P28">
-        <v>27.16625472799999</v>
+        <v>26.77513375599999</v>
       </c>
       <c r="Q28">
-        <v>27.63625472799999</v>
+        <v>27.24513375599999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09832710822963633</v>
+        <v>0.09886080544921116</v>
       </c>
       <c r="T28">
-        <v>0.6846043069338738</v>
+        <v>0.6915601708189032</v>
       </c>
       <c r="U28">
         <v>0.0613</v>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.671439339430059</v>
+        <v>3.535460104636353</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08342306797792415</v>
+        <v>0.08377935586591742</v>
       </c>
       <c r="C29">
-        <v>734.4649871724336</v>
+        <v>716.3415662034132</v>
       </c>
       <c r="D29">
-        <v>931.7059871724335</v>
+        <v>922.9655662034132</v>
       </c>
       <c r="E29">
-        <v>-89.75899999999999</v>
+        <v>-80.37599999999998</v>
       </c>
       <c r="F29">
-        <v>253.341</v>
+        <v>262.724</v>
       </c>
       <c r="G29">
         <v>56.1</v>
@@ -3793,45 +3793,45 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M29">
-        <v>15.5298033</v>
+        <v>16.8406084</v>
       </c>
       <c r="N29">
-        <v>39.37519669999999</v>
+        <v>38.06439159999999</v>
       </c>
       <c r="O29">
-        <v>12.600062944</v>
+        <v>12.180605312</v>
       </c>
       <c r="P29">
-        <v>26.77513375599999</v>
+        <v>25.883786288</v>
       </c>
       <c r="Q29">
-        <v>27.24513375599999</v>
+        <v>26.35378628799999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09886080544921116</v>
+        <v>0.09940932759155197</v>
       </c>
       <c r="T29">
-        <v>0.6915601708189032</v>
+        <v>0.6987092531451835</v>
       </c>
       <c r="U29">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V29">
         <v>0.32</v>
       </c>
       <c r="W29">
-        <v>0.041684</v>
+        <v>0.043588</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>3.535460104636353</v>
+        <v>3.260274135939173</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08377935586591742</v>
+        <v>0.08362156375391067</v>
       </c>
       <c r="C30">
-        <v>716.3415662034132</v>
+        <v>710.809191919165</v>
       </c>
       <c r="D30">
-        <v>922.9655662034132</v>
+        <v>926.8161919191649</v>
       </c>
       <c r="E30">
-        <v>-80.37599999999998</v>
+        <v>-70.99299999999999</v>
       </c>
       <c r="F30">
-        <v>262.724</v>
+        <v>272.107</v>
       </c>
       <c r="G30">
         <v>56.1</v>
@@ -3875,28 +3875,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M30">
-        <v>16.8406084</v>
+        <v>17.4420587</v>
       </c>
       <c r="N30">
-        <v>38.06439159999999</v>
+        <v>37.46294129999999</v>
       </c>
       <c r="O30">
-        <v>12.180605312</v>
+        <v>11.988141216</v>
       </c>
       <c r="P30">
-        <v>25.883786288</v>
+        <v>25.47480008399999</v>
       </c>
       <c r="Q30">
-        <v>26.35378628799999</v>
+        <v>25.94480008399999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09940932759155197</v>
+        <v>0.09997330106184601</v>
       </c>
       <c r="T30">
-        <v>0.6987092531451835</v>
+        <v>0.706059718072204</v>
       </c>
       <c r="U30">
         <v>0.0641</v>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.260274135939173</v>
+        <v>3.147850889872305</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08362156375391067</v>
+        <v>0.08346377164190392</v>
       </c>
       <c r="C31">
-        <v>710.809191919165</v>
+        <v>705.3090819747708</v>
       </c>
       <c r="D31">
-        <v>926.8161919191649</v>
+        <v>930.6990819747708</v>
       </c>
       <c r="E31">
-        <v>-70.99299999999999</v>
+        <v>-61.61000000000001</v>
       </c>
       <c r="F31">
-        <v>272.107</v>
+        <v>281.49</v>
       </c>
       <c r="G31">
         <v>56.1</v>
@@ -3957,28 +3957,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M31">
-        <v>17.4420587</v>
+        <v>18.043509</v>
       </c>
       <c r="N31">
-        <v>37.46294129999999</v>
+        <v>36.86149099999999</v>
       </c>
       <c r="O31">
-        <v>11.988141216</v>
+        <v>11.79567712</v>
       </c>
       <c r="P31">
-        <v>25.47480008399999</v>
+        <v>25.06581387999999</v>
       </c>
       <c r="Q31">
-        <v>25.94480008399999</v>
+        <v>25.53581387999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09997330106184601</v>
+        <v>0.1005533880598627</v>
       </c>
       <c r="T31">
-        <v>0.706059718072204</v>
+        <v>0.7136201962828537</v>
       </c>
       <c r="U31">
         <v>0.0641</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.147850889872305</v>
+        <v>3.042922526876562</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08346377164190392</v>
+        <v>0.08495021952989718</v>
       </c>
       <c r="C32">
-        <v>705.3090819747708</v>
+        <v>660.5894810215581</v>
       </c>
       <c r="D32">
-        <v>930.6990819747708</v>
+        <v>895.3624810215581</v>
       </c>
       <c r="E32">
-        <v>-61.61000000000001</v>
+        <v>-52.22699999999998</v>
       </c>
       <c r="F32">
-        <v>281.49</v>
+        <v>290.873</v>
       </c>
       <c r="G32">
         <v>56.1</v>
@@ -4039,45 +4039,45 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M32">
-        <v>18.043509</v>
+        <v>20.91376870000001</v>
       </c>
       <c r="N32">
-        <v>36.86149099999999</v>
+        <v>33.99123129999999</v>
       </c>
       <c r="O32">
-        <v>11.79567712</v>
+        <v>10.877194016</v>
       </c>
       <c r="P32">
-        <v>25.06581387999999</v>
+        <v>23.11403728399999</v>
       </c>
       <c r="Q32">
-        <v>25.53581387999999</v>
+        <v>23.58403728399999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1005533880598627</v>
+        <v>0.101150289173764</v>
       </c>
       <c r="T32">
-        <v>0.7136201962828537</v>
+        <v>0.7213998187894644</v>
       </c>
       <c r="U32">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V32">
         <v>0.32</v>
       </c>
       <c r="W32">
-        <v>0.043588</v>
+        <v>0.048892</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>3.042922526876562</v>
+        <v>2.625303970202175</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08495021952989718</v>
+        <v>0.08484546741789044</v>
       </c>
       <c r="C33">
-        <v>660.5894810215581</v>
+        <v>653.6085808580074</v>
       </c>
       <c r="D33">
-        <v>895.3624810215581</v>
+        <v>897.7645808580074</v>
       </c>
       <c r="E33">
-        <v>-52.22699999999998</v>
+        <v>-42.84399999999999</v>
       </c>
       <c r="F33">
-        <v>290.873</v>
+        <v>300.256</v>
       </c>
       <c r="G33">
         <v>56.1</v>
@@ -4121,28 +4121,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M33">
-        <v>20.91376870000001</v>
+        <v>21.5884064</v>
       </c>
       <c r="N33">
-        <v>33.99123129999999</v>
+        <v>33.31659359999999</v>
       </c>
       <c r="O33">
-        <v>10.877194016</v>
+        <v>10.661309952</v>
       </c>
       <c r="P33">
-        <v>23.11403728399999</v>
+        <v>22.65528364799999</v>
       </c>
       <c r="Q33">
-        <v>23.58403728399999</v>
+        <v>23.12528364799999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.101150289173764</v>
+        <v>0.1017647462027801</v>
       </c>
       <c r="T33">
-        <v>0.7213998187894644</v>
+        <v>0.7294082537227399</v>
       </c>
       <c r="U33">
         <v>0.07190000000000001</v>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.625303970202175</v>
+        <v>2.543263221133357</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08484546741789044</v>
+        <v>0.0856158753058837</v>
       </c>
       <c r="C34">
-        <v>653.6085808580074</v>
+        <v>626.8544968534378</v>
       </c>
       <c r="D34">
-        <v>897.7645808580074</v>
+        <v>880.3934968534378</v>
       </c>
       <c r="E34">
-        <v>-42.84399999999999</v>
+        <v>-33.46100000000001</v>
       </c>
       <c r="F34">
-        <v>300.256</v>
+        <v>309.639</v>
       </c>
       <c r="G34">
         <v>56.1</v>
@@ -4203,45 +4203,45 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M34">
-        <v>21.5884064</v>
+        <v>23.4706362</v>
       </c>
       <c r="N34">
-        <v>33.31659359999999</v>
+        <v>31.43436379999999</v>
       </c>
       <c r="O34">
-        <v>10.661309952</v>
+        <v>10.058996416</v>
       </c>
       <c r="P34">
-        <v>22.65528364799999</v>
+        <v>21.37536738399999</v>
       </c>
       <c r="Q34">
-        <v>23.12528364799999</v>
+        <v>21.84536738399999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1017647462027801</v>
+        <v>0.1023975452326623</v>
       </c>
       <c r="T34">
-        <v>0.7294082537227399</v>
+        <v>0.7376557464152178</v>
       </c>
       <c r="U34">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V34">
         <v>0.32</v>
       </c>
       <c r="W34">
-        <v>0.048892</v>
+        <v>0.051544</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y34">
-        <v>2.543263221133357</v>
+        <v>2.339305996315515</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0856158753058837</v>
+        <v>0.08553764319387697</v>
       </c>
       <c r="C35">
-        <v>626.8544968534378</v>
+        <v>619.2047411306538</v>
       </c>
       <c r="D35">
-        <v>880.3934968534378</v>
+        <v>882.1267411306538</v>
       </c>
       <c r="E35">
-        <v>-33.46100000000001</v>
+        <v>-24.07799999999997</v>
       </c>
       <c r="F35">
-        <v>309.639</v>
+        <v>319.022</v>
       </c>
       <c r="G35">
         <v>56.1</v>
@@ -4285,28 +4285,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M35">
-        <v>23.4706362</v>
+        <v>24.1818676</v>
       </c>
       <c r="N35">
-        <v>31.43436379999999</v>
+        <v>30.72313239999999</v>
       </c>
       <c r="O35">
-        <v>10.058996416</v>
+        <v>9.831402367999997</v>
       </c>
       <c r="P35">
-        <v>21.37536738399999</v>
+        <v>20.89173003199999</v>
       </c>
       <c r="Q35">
-        <v>21.84536738399999</v>
+        <v>21.36173003199999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1023975452326623</v>
+        <v>0.1030495199907227</v>
       </c>
       <c r="T35">
-        <v>0.7376557464152178</v>
+        <v>0.7461531631286797</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.339305996315515</v>
+        <v>2.270502878776823</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08553764319387697</v>
+        <v>0.08545941108187022</v>
       </c>
       <c r="C36">
-        <v>619.2047411306538</v>
+        <v>611.561823399496</v>
       </c>
       <c r="D36">
-        <v>882.1267411306538</v>
+        <v>883.866823399496</v>
       </c>
       <c r="E36">
-        <v>-24.07799999999997</v>
+        <v>-14.69499999999999</v>
       </c>
       <c r="F36">
-        <v>319.022</v>
+        <v>328.405</v>
       </c>
       <c r="G36">
         <v>56.1</v>
@@ -4367,28 +4367,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M36">
-        <v>24.1818676</v>
+        <v>24.893099</v>
       </c>
       <c r="N36">
-        <v>30.72313239999999</v>
+        <v>30.01190099999999</v>
       </c>
       <c r="O36">
-        <v>9.831402367999997</v>
+        <v>9.603808319999997</v>
       </c>
       <c r="P36">
-        <v>20.89173003199999</v>
+        <v>20.40809268</v>
       </c>
       <c r="Q36">
-        <v>21.36173003199999</v>
+        <v>20.87809267999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1030495199907227</v>
+        <v>0.1037215555105696</v>
       </c>
       <c r="T36">
-        <v>0.7461531631286797</v>
+        <v>0.7549120388179407</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.270502878776823</v>
+        <v>2.205631367954628</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08545941108187022</v>
+        <v>0.08538117896986348</v>
       </c>
       <c r="C37">
-        <v>611.561823399496</v>
+        <v>603.9257842057891</v>
       </c>
       <c r="D37">
-        <v>883.866823399496</v>
+        <v>885.6137842057891</v>
       </c>
       <c r="E37">
-        <v>-14.69499999999999</v>
+        <v>-5.311999999999955</v>
       </c>
       <c r="F37">
-        <v>328.405</v>
+        <v>337.7880000000001</v>
       </c>
       <c r="G37">
         <v>56.1</v>
@@ -4449,28 +4449,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M37">
-        <v>24.893099</v>
+        <v>25.60433040000001</v>
       </c>
       <c r="N37">
-        <v>30.01190099999999</v>
+        <v>29.30066959999999</v>
       </c>
       <c r="O37">
-        <v>9.603808319999997</v>
+        <v>9.376214271999997</v>
       </c>
       <c r="P37">
-        <v>20.40809268</v>
+        <v>19.92445532799999</v>
       </c>
       <c r="Q37">
-        <v>20.87809267999999</v>
+        <v>20.39445532799999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1037215555105696</v>
+        <v>0.1044145921404117</v>
       </c>
       <c r="T37">
-        <v>0.7549120388179407</v>
+        <v>0.7639446293724909</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.205631367954628</v>
+        <v>2.144363829955888</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0853811789698635</v>
+        <v>0.08530294685785675</v>
       </c>
       <c r="C38">
-        <v>603.9257842057887</v>
+        <v>596.296664416549</v>
       </c>
       <c r="D38">
-        <v>885.6137842057886</v>
+        <v>887.367664416549</v>
       </c>
       <c r="E38">
-        <v>-5.312000000000012</v>
+        <v>4.071000000000026</v>
       </c>
       <c r="F38">
-        <v>337.788</v>
+        <v>347.171</v>
       </c>
       <c r="G38">
         <v>56.1</v>
@@ -4531,28 +4531,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M38">
-        <v>25.6043304</v>
+        <v>26.3155618</v>
       </c>
       <c r="N38">
-        <v>29.30066959999999</v>
+        <v>28.58943819999999</v>
       </c>
       <c r="O38">
-        <v>9.376214271999997</v>
+        <v>9.148620223999997</v>
       </c>
       <c r="P38">
-        <v>19.92445532799999</v>
+        <v>19.44081797599999</v>
       </c>
       <c r="Q38">
-        <v>20.39445532799999</v>
+        <v>19.91081797599999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1044145921404117</v>
+        <v>0.105129629933106</v>
       </c>
       <c r="T38">
-        <v>0.7639446293724907</v>
+        <v>0.7732639688335348</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.144363829955889</v>
+        <v>2.086408050767892</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08530294685785675</v>
+        <v>0.08522471474585001</v>
       </c>
       <c r="C39">
-        <v>596.296664416549</v>
+        <v>588.6745052231674</v>
       </c>
       <c r="D39">
-        <v>887.367664416549</v>
+        <v>889.1285052231675</v>
       </c>
       <c r="E39">
-        <v>4.071000000000026</v>
+        <v>13.45400000000001</v>
       </c>
       <c r="F39">
-        <v>347.171</v>
+        <v>356.554</v>
       </c>
       <c r="G39">
         <v>56.1</v>
@@ -4613,28 +4613,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M39">
-        <v>26.3155618</v>
+        <v>27.0267932</v>
       </c>
       <c r="N39">
-        <v>28.58943819999999</v>
+        <v>27.87820679999999</v>
       </c>
       <c r="O39">
-        <v>9.148620223999997</v>
+        <v>8.921026175999996</v>
       </c>
       <c r="P39">
-        <v>19.44081797599999</v>
+        <v>18.957180624</v>
       </c>
       <c r="Q39">
-        <v>19.91081797599999</v>
+        <v>19.42718062399999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.105129629933106</v>
+        <v>0.1058677334610484</v>
       </c>
       <c r="T39">
-        <v>0.7732639688335348</v>
+        <v>0.7828839321481607</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.086408050767892</v>
+        <v>2.031502575747684</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08522471474585001</v>
+        <v>0.08891232263384327</v>
       </c>
       <c r="C40">
-        <v>588.6745052231674</v>
+        <v>503.2399939847827</v>
       </c>
       <c r="D40">
-        <v>889.1285052231675</v>
+        <v>813.0769939847827</v>
       </c>
       <c r="E40">
-        <v>13.45400000000001</v>
+        <v>22.83699999999999</v>
       </c>
       <c r="F40">
-        <v>356.554</v>
+        <v>365.937</v>
       </c>
       <c r="G40">
         <v>56.1</v>
@@ -4695,45 +4695,45 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M40">
-        <v>27.0267932</v>
+        <v>32.93433</v>
       </c>
       <c r="N40">
-        <v>27.87820679999999</v>
+        <v>21.97066999999999</v>
       </c>
       <c r="O40">
-        <v>8.921026175999996</v>
+        <v>7.030614399999997</v>
       </c>
       <c r="P40">
-        <v>18.957180624</v>
+        <v>14.94005559999999</v>
       </c>
       <c r="Q40">
-        <v>19.42718062399999</v>
+        <v>15.41005559999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1058677334610484</v>
+        <v>0.1066300371046611</v>
       </c>
       <c r="T40">
-        <v>0.7828839321481607</v>
+        <v>0.7928193040960531</v>
       </c>
       <c r="U40">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V40">
         <v>0.32</v>
       </c>
       <c r="W40">
-        <v>0.051544</v>
+        <v>0.06119999999999999</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y40">
-        <v>2.031502575747684</v>
+        <v>1.667105418570834</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08891232263384327</v>
+        <v>0.08893065052183653</v>
       </c>
       <c r="C41">
-        <v>503.2399939847827</v>
+        <v>493.5114860015885</v>
       </c>
       <c r="D41">
-        <v>813.0769939847827</v>
+        <v>812.7314860015886</v>
       </c>
       <c r="E41">
-        <v>22.83699999999999</v>
+        <v>32.22000000000003</v>
       </c>
       <c r="F41">
-        <v>365.937</v>
+        <v>375.3200000000001</v>
       </c>
       <c r="G41">
         <v>56.1</v>
@@ -4777,28 +4777,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M41">
-        <v>32.93433</v>
+        <v>33.7788</v>
       </c>
       <c r="N41">
-        <v>21.97066999999999</v>
+        <v>21.12619999999999</v>
       </c>
       <c r="O41">
-        <v>7.030614399999997</v>
+        <v>6.760383999999997</v>
       </c>
       <c r="P41">
-        <v>14.94005559999999</v>
+        <v>14.36581599999999</v>
       </c>
       <c r="Q41">
-        <v>15.41005559999999</v>
+        <v>14.83581599999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1066300371046611</v>
+        <v>0.1074177508697275</v>
       </c>
       <c r="T41">
-        <v>0.7928193040960531</v>
+        <v>0.8030858551088752</v>
       </c>
       <c r="U41">
         <v>0.09</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>1.667105418570834</v>
+        <v>1.625427783106564</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08893065052183653</v>
+        <v>0.08894897840982979</v>
       </c>
       <c r="C42">
-        <v>493.5114860015885</v>
+        <v>483.7832715331819</v>
       </c>
       <c r="D42">
-        <v>812.7314860015886</v>
+        <v>812.3862715331819</v>
       </c>
       <c r="E42">
-        <v>32.22000000000003</v>
+        <v>41.60300000000001</v>
       </c>
       <c r="F42">
-        <v>375.3200000000001</v>
+        <v>384.703</v>
       </c>
       <c r="G42">
         <v>56.1</v>
@@ -4859,28 +4859,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M42">
-        <v>33.7788</v>
+        <v>34.62327</v>
       </c>
       <c r="N42">
-        <v>21.12619999999999</v>
+        <v>20.28173</v>
       </c>
       <c r="O42">
-        <v>6.760383999999997</v>
+        <v>6.490153599999999</v>
       </c>
       <c r="P42">
-        <v>14.36581599999999</v>
+        <v>13.7915764</v>
       </c>
       <c r="Q42">
-        <v>14.83581599999999</v>
+        <v>14.2615764</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1074177508697275</v>
+        <v>0.1082321667963217</v>
       </c>
       <c r="T42">
-        <v>0.8030858551088752</v>
+        <v>0.8137004248000981</v>
       </c>
       <c r="U42">
         <v>0.09</v>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.625427783106564</v>
+        <v>1.585783203030794</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08894897840982979</v>
+        <v>0.08896730629782304</v>
       </c>
       <c r="C43">
-        <v>483.7832715331819</v>
+        <v>474.0553502057035</v>
       </c>
       <c r="D43">
-        <v>812.3862715331819</v>
+        <v>812.0413502057036</v>
       </c>
       <c r="E43">
-        <v>41.60300000000001</v>
+        <v>50.98600000000005</v>
       </c>
       <c r="F43">
-        <v>384.703</v>
+        <v>394.0860000000001</v>
       </c>
       <c r="G43">
         <v>56.1</v>
@@ -4941,28 +4941,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M43">
-        <v>34.62327</v>
+        <v>35.46774000000001</v>
       </c>
       <c r="N43">
-        <v>20.28173</v>
+        <v>19.43725999999999</v>
       </c>
       <c r="O43">
-        <v>6.490153599999999</v>
+        <v>6.219923199999997</v>
       </c>
       <c r="P43">
-        <v>13.7915764</v>
+        <v>13.21733679999999</v>
       </c>
       <c r="Q43">
-        <v>14.2615764</v>
+        <v>13.68733679999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1082321667963217</v>
+        <v>0.1090746660307294</v>
       </c>
       <c r="T43">
-        <v>0.8137004248000981</v>
+        <v>0.8246810141358459</v>
       </c>
       <c r="U43">
         <v>0.09</v>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.585783203030794</v>
+        <v>1.548026460101489</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08896730629782305</v>
+        <v>0.08898563418581631</v>
       </c>
       <c r="C44">
-        <v>474.0553502057033</v>
+        <v>464.3277216459275</v>
       </c>
       <c r="D44">
-        <v>812.0413502057033</v>
+        <v>811.6967216459275</v>
       </c>
       <c r="E44">
-        <v>50.98599999999999</v>
+        <v>60.36900000000003</v>
       </c>
       <c r="F44">
-        <v>394.086</v>
+        <v>403.4690000000001</v>
       </c>
       <c r="G44">
         <v>56.1</v>
@@ -5023,28 +5023,28 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M44">
-        <v>35.46774</v>
+        <v>36.31221</v>
       </c>
       <c r="N44">
-        <v>19.43725999999999</v>
+        <v>18.59278999999999</v>
       </c>
       <c r="O44">
-        <v>6.219923199999998</v>
+        <v>5.949692799999998</v>
       </c>
       <c r="P44">
-        <v>13.2173368</v>
+        <v>12.6430972</v>
       </c>
       <c r="Q44">
-        <v>13.6873368</v>
+        <v>13.1130972</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1090746660307294</v>
+        <v>0.109946726641783</v>
       </c>
       <c r="T44">
-        <v>0.8246810141358459</v>
+        <v>0.8360468873079357</v>
       </c>
       <c r="U44">
         <v>0.09</v>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.548026460101489</v>
+        <v>1.512025844750292</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08898563418581631</v>
+        <v>0.1085046315122812</v>
       </c>
       <c r="C45">
-        <v>464.3277216459275</v>
+        <v>202.2758875008118</v>
       </c>
       <c r="D45">
-        <v>811.6967216459275</v>
+        <v>559.0278875008119</v>
       </c>
       <c r="E45">
-        <v>60.36900000000003</v>
+        <v>69.75200000000001</v>
       </c>
       <c r="F45">
-        <v>403.4690000000001</v>
+        <v>412.852</v>
       </c>
       <c r="G45">
         <v>56.1</v>
@@ -5105,45 +5105,45 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M45">
-        <v>36.31221</v>
+        <v>60.60667360000001</v>
       </c>
       <c r="N45">
-        <v>18.59278999999999</v>
+        <v>-5.701673600000014</v>
       </c>
       <c r="O45">
-        <v>5.949692799999998</v>
+        <v>-1.824535552000004</v>
       </c>
       <c r="P45">
-        <v>12.6430972</v>
+        <v>-3.877138048000009</v>
       </c>
       <c r="Q45">
-        <v>13.1130972</v>
+        <v>-3.407138048000009</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.109946726641783</v>
+        <v>0.11185278495298</v>
       </c>
       <c r="T45">
-        <v>0.8360468873079357</v>
+        <v>0.8608892167848955</v>
       </c>
       <c r="U45">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.32</v>
+        <v>0.2898954678812796</v>
       </c>
       <c r="W45">
-        <v>0.06119999999999999</v>
+        <v>0.1042433453150282</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y45">
-        <v>1.512025844750292</v>
+        <v>0.9059233371289988</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1085046315122812</v>
+        <v>0.1095146315122812</v>
       </c>
       <c r="C46">
-        <v>202.2758875008118</v>
+        <v>184.0312154958974</v>
       </c>
       <c r="D46">
-        <v>559.0278875008119</v>
+        <v>550.1662154958974</v>
       </c>
       <c r="E46">
-        <v>69.75200000000001</v>
+        <v>79.13499999999999</v>
       </c>
       <c r="F46">
-        <v>412.852</v>
+        <v>422.235</v>
       </c>
       <c r="G46">
         <v>56.1</v>
@@ -5187,37 +5187,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M46">
-        <v>60.60667360000001</v>
+        <v>61.98409800000001</v>
       </c>
       <c r="N46">
-        <v>-5.701673600000014</v>
+        <v>-7.079098000000016</v>
       </c>
       <c r="O46">
-        <v>-1.824535552000004</v>
+        <v>-2.265311360000005</v>
       </c>
       <c r="P46">
-        <v>-3.877138048000009</v>
+        <v>-4.813786640000011</v>
       </c>
       <c r="Q46">
-        <v>-3.407138048000009</v>
+        <v>-4.343786640000011</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.11185278495298</v>
+        <v>0.1130537446793978</v>
       </c>
       <c r="T46">
-        <v>0.8608892167848955</v>
+        <v>0.8765417479991663</v>
       </c>
       <c r="U46">
         <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.2898954678812796</v>
+        <v>0.2834533463728067</v>
       </c>
       <c r="W46">
-        <v>0.1042433453150282</v>
+        <v>0.105189048752472</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.9059233371289988</v>
+        <v>0.885791707415021</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1095146315122812</v>
+        <v>0.1105246315122812</v>
       </c>
       <c r="C47">
-        <v>184.0312154958974</v>
+        <v>166.0631086414008</v>
       </c>
       <c r="D47">
-        <v>550.1662154958974</v>
+        <v>541.5811086414009</v>
       </c>
       <c r="E47">
-        <v>79.13499999999999</v>
+        <v>88.51800000000003</v>
       </c>
       <c r="F47">
-        <v>422.235</v>
+        <v>431.6180000000001</v>
       </c>
       <c r="G47">
         <v>56.1</v>
@@ -5269,37 +5269,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M47">
-        <v>61.98409800000001</v>
+        <v>63.36152240000001</v>
       </c>
       <c r="N47">
-        <v>-7.079098000000016</v>
+        <v>-8.456522400000019</v>
       </c>
       <c r="O47">
-        <v>-2.265311360000005</v>
+        <v>-2.706087168000006</v>
       </c>
       <c r="P47">
-        <v>-4.813786640000011</v>
+        <v>-5.750435232000012</v>
       </c>
       <c r="Q47">
-        <v>-4.343786640000011</v>
+        <v>-5.280435232000013</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1130537446793978</v>
+        <v>0.1142991843956829</v>
       </c>
       <c r="T47">
-        <v>0.8765417479991663</v>
+        <v>0.8927740025917434</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.2834533463728067</v>
+        <v>0.2772913171038326</v>
       </c>
       <c r="W47">
-        <v>0.105189048752472</v>
+        <v>0.1060936346491574</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.885791707415021</v>
+        <v>0.866535365949477</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1105246315122812</v>
+        <v>0.1115346315122812</v>
       </c>
       <c r="C48">
-        <v>166.0631086414008</v>
+        <v>148.3588188259156</v>
       </c>
       <c r="D48">
-        <v>541.5811086414009</v>
+        <v>533.2598188259157</v>
       </c>
       <c r="E48">
-        <v>88.51800000000003</v>
+        <v>97.90100000000001</v>
       </c>
       <c r="F48">
-        <v>431.6180000000001</v>
+        <v>441.001</v>
       </c>
       <c r="G48">
         <v>56.1</v>
@@ -5351,37 +5351,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M48">
-        <v>63.36152240000001</v>
+        <v>64.73894680000001</v>
       </c>
       <c r="N48">
-        <v>-8.456522400000019</v>
+        <v>-9.833946800000014</v>
       </c>
       <c r="O48">
-        <v>-2.706087168000006</v>
+        <v>-3.146862976000004</v>
       </c>
       <c r="P48">
-        <v>-5.750435232000012</v>
+        <v>-6.687083824000009</v>
       </c>
       <c r="Q48">
-        <v>-5.280435232000013</v>
+        <v>-6.217083824000009</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1142991843956829</v>
+        <v>0.1155916218371109</v>
       </c>
       <c r="T48">
-        <v>0.8927740025917434</v>
+        <v>0.9096187950934744</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.2772913171038326</v>
+        <v>0.2713915018463043</v>
       </c>
       <c r="W48">
-        <v>0.1060936346491574</v>
+        <v>0.1069597275289625</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.866535365949477</v>
+        <v>0.848098443269701</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1115346315122812</v>
+        <v>0.1125446315122812</v>
       </c>
       <c r="C49">
-        <v>148.3588188259156</v>
+        <v>130.906369571183</v>
       </c>
       <c r="D49">
-        <v>533.2598188259157</v>
+        <v>525.1903695711831</v>
       </c>
       <c r="E49">
-        <v>97.90100000000001</v>
+        <v>107.284</v>
       </c>
       <c r="F49">
-        <v>441.001</v>
+        <v>450.3840000000001</v>
       </c>
       <c r="G49">
         <v>56.1</v>
@@ -5433,37 +5433,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M49">
-        <v>64.73894680000001</v>
+        <v>66.11637120000002</v>
       </c>
       <c r="N49">
-        <v>-9.833946800000014</v>
+        <v>-11.21137120000002</v>
       </c>
       <c r="O49">
-        <v>-3.146862976000004</v>
+        <v>-3.587638784000008</v>
       </c>
       <c r="P49">
-        <v>-6.687083824000009</v>
+        <v>-7.623732416000015</v>
       </c>
       <c r="Q49">
-        <v>-6.217083824000009</v>
+        <v>-7.153732416000016</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1155916218371109</v>
+        <v>0.1169337684109015</v>
       </c>
       <c r="T49">
-        <v>0.9096187950934744</v>
+        <v>0.9271114642298875</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.2713915018463043</v>
+        <v>0.2657375122245063</v>
       </c>
       <c r="W49">
-        <v>0.1069597275289625</v>
+        <v>0.1077897332054425</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.848098443269701</v>
+        <v>0.830429725701582</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1125446315122812</v>
+        <v>0.1135546315122812</v>
       </c>
       <c r="C50">
-        <v>130.9063695711833</v>
+        <v>113.6944985194566</v>
       </c>
       <c r="D50">
-        <v>525.1903695711833</v>
+        <v>517.3614985194566</v>
       </c>
       <c r="E50">
-        <v>107.284</v>
+        <v>116.667</v>
       </c>
       <c r="F50">
-        <v>450.384</v>
+        <v>459.7670000000001</v>
       </c>
       <c r="G50">
         <v>56.1</v>
@@ -5515,37 +5515,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M50">
-        <v>66.1163712</v>
+        <v>67.49379560000001</v>
       </c>
       <c r="N50">
-        <v>-11.21137120000001</v>
+        <v>-12.58879560000002</v>
       </c>
       <c r="O50">
-        <v>-3.587638784000003</v>
+        <v>-4.028414592000006</v>
       </c>
       <c r="P50">
-        <v>-7.623732416000006</v>
+        <v>-8.560381008000013</v>
       </c>
       <c r="Q50">
-        <v>-7.153732416000007</v>
+        <v>-8.090381008000012</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1169337684109015</v>
+        <v>0.1183285481836643</v>
       </c>
       <c r="T50">
-        <v>0.9271114642298874</v>
+        <v>0.9452901203912578</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.2657375122245063</v>
+        <v>0.2603142976893122</v>
       </c>
       <c r="W50">
-        <v>0.1077897332054425</v>
+        <v>0.108585861099209</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8304297257015822</v>
+        <v>0.8134821802791008</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1135546315122812</v>
+        <v>0.1430189675338729</v>
       </c>
       <c r="C51">
-        <v>113.6944985194566</v>
+        <v>-52.48622751790634</v>
       </c>
       <c r="D51">
-        <v>517.3614985194566</v>
+        <v>360.5637724820937</v>
       </c>
       <c r="E51">
-        <v>116.667</v>
+        <v>126.05</v>
       </c>
       <c r="F51">
-        <v>459.7670000000001</v>
+        <v>469.15</v>
       </c>
       <c r="G51">
         <v>56.1</v>
@@ -5597,45 +5597,45 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M51">
-        <v>67.49379560000001</v>
+        <v>94.20532000000001</v>
       </c>
       <c r="N51">
-        <v>-12.58879560000002</v>
+        <v>-39.30032000000002</v>
       </c>
       <c r="O51">
-        <v>-4.028414592000006</v>
+        <v>-12.57610240000001</v>
       </c>
       <c r="P51">
-        <v>-8.560381008000013</v>
+        <v>-26.72421760000001</v>
       </c>
       <c r="Q51">
-        <v>-8.090381008000012</v>
+        <v>-26.25421760000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1183285481836643</v>
+        <v>0.122687791190521</v>
       </c>
       <c r="T51">
-        <v>0.9452901203912578</v>
+        <v>1.002105670267306</v>
       </c>
       <c r="U51">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.2603142976893122</v>
+        <v>0.1865032675437013</v>
       </c>
       <c r="W51">
-        <v>0.108585861099209</v>
+        <v>0.1633501438772248</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y51">
-        <v>0.8134821802791008</v>
+        <v>0.5828227110740666</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1430189675338729</v>
+        <v>0.1445689675338729</v>
       </c>
       <c r="C52">
-        <v>-52.48622751790634</v>
+        <v>-67.52762267279724</v>
       </c>
       <c r="D52">
-        <v>360.5637724820937</v>
+        <v>354.9053773272028</v>
       </c>
       <c r="E52">
-        <v>126.05</v>
+        <v>135.433</v>
       </c>
       <c r="F52">
-        <v>469.15</v>
+        <v>478.533</v>
       </c>
       <c r="G52">
         <v>56.1</v>
@@ -5679,37 +5679,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M52">
-        <v>94.20532000000001</v>
+        <v>96.08942640000001</v>
       </c>
       <c r="N52">
-        <v>-39.30032000000002</v>
+        <v>-41.18442640000001</v>
       </c>
       <c r="O52">
-        <v>-12.57610240000001</v>
+        <v>-13.179016448</v>
       </c>
       <c r="P52">
-        <v>-26.72421760000001</v>
+        <v>-28.00540995200001</v>
       </c>
       <c r="Q52">
-        <v>-26.25421760000001</v>
+        <v>-27.53540995200001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.122687791190521</v>
+        <v>0.1242569297862459</v>
       </c>
       <c r="T52">
-        <v>1.002105670267306</v>
+        <v>1.02255680639521</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.1865032675437013</v>
+        <v>0.182846340729119</v>
       </c>
       <c r="W52">
-        <v>0.1633501438772248</v>
+        <v>0.1640844547815929</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5828227110740666</v>
+        <v>0.5713948147784966</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1445689675338729</v>
+        <v>0.1461189675338729</v>
       </c>
       <c r="C53">
-        <v>-67.52762267279724</v>
+        <v>-82.39416530067996</v>
       </c>
       <c r="D53">
-        <v>354.9053773272028</v>
+        <v>349.4218346993201</v>
       </c>
       <c r="E53">
-        <v>135.433</v>
+        <v>144.816</v>
       </c>
       <c r="F53">
-        <v>478.533</v>
+        <v>487.9160000000001</v>
       </c>
       <c r="G53">
         <v>56.1</v>
@@ -5761,37 +5761,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M53">
-        <v>96.08942640000001</v>
+        <v>97.97353280000002</v>
       </c>
       <c r="N53">
-        <v>-41.18442640000001</v>
+        <v>-43.06853280000002</v>
       </c>
       <c r="O53">
-        <v>-13.179016448</v>
+        <v>-13.78193049600001</v>
       </c>
       <c r="P53">
-        <v>-28.00540995200001</v>
+        <v>-29.28660230400001</v>
       </c>
       <c r="Q53">
-        <v>-27.53540995200001</v>
+        <v>-28.81660230400001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1242569297862459</v>
+        <v>0.1258914491567927</v>
       </c>
       <c r="T53">
-        <v>1.02255680639521</v>
+        <v>1.04386007319511</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.182846340729119</v>
+        <v>0.1793300649458666</v>
       </c>
       <c r="W53">
-        <v>0.1640844547815929</v>
+        <v>0.16479052295887</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5713948147784966</v>
+        <v>0.5604064529558332</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1461189675338729</v>
+        <v>0.1476689675338729</v>
       </c>
       <c r="C54">
-        <v>-82.39416530067996</v>
+        <v>-97.09383687295099</v>
       </c>
       <c r="D54">
-        <v>349.4218346993201</v>
+        <v>344.105163127049</v>
       </c>
       <c r="E54">
-        <v>144.816</v>
+        <v>154.199</v>
       </c>
       <c r="F54">
-        <v>487.9160000000001</v>
+        <v>497.299</v>
       </c>
       <c r="G54">
         <v>56.1</v>
@@ -5843,37 +5843,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M54">
-        <v>97.97353280000002</v>
+        <v>99.85763920000001</v>
       </c>
       <c r="N54">
-        <v>-43.06853280000002</v>
+        <v>-44.95263920000001</v>
       </c>
       <c r="O54">
-        <v>-13.78193049600001</v>
+        <v>-14.38484454400001</v>
       </c>
       <c r="P54">
-        <v>-29.28660230400001</v>
+        <v>-30.56779465600001</v>
       </c>
       <c r="Q54">
-        <v>-28.81660230400001</v>
+        <v>-30.09779465600001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1258914491567927</v>
+        <v>0.1275955225431074</v>
       </c>
       <c r="T54">
-        <v>1.04386007319511</v>
+        <v>1.066069861986495</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1793300649458666</v>
+        <v>0.1759464788148126</v>
       </c>
       <c r="W54">
-        <v>0.16479052295887</v>
+        <v>0.1654699470539856</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5604064529558332</v>
+        <v>0.5498327462962893</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1476689675338729</v>
+        <v>0.1492189675338729</v>
       </c>
       <c r="C55">
-        <v>-97.09383687295099</v>
+        <v>-111.6341403692583</v>
       </c>
       <c r="D55">
-        <v>344.105163127049</v>
+        <v>338.9478596307417</v>
       </c>
       <c r="E55">
-        <v>154.199</v>
+        <v>163.5820000000001</v>
       </c>
       <c r="F55">
-        <v>497.299</v>
+        <v>506.6820000000001</v>
       </c>
       <c r="G55">
         <v>56.1</v>
@@ -5925,37 +5925,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M55">
-        <v>99.85763920000001</v>
+        <v>101.7417456</v>
       </c>
       <c r="N55">
-        <v>-44.95263920000001</v>
+        <v>-46.83674560000002</v>
       </c>
       <c r="O55">
-        <v>-14.38484454400001</v>
+        <v>-14.98775859200001</v>
       </c>
       <c r="P55">
-        <v>-30.56779465600001</v>
+        <v>-31.84898700800002</v>
       </c>
       <c r="Q55">
-        <v>-30.09779465600001</v>
+        <v>-31.37898700800002</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1275955225431074</v>
+        <v>0.1293736860766533</v>
       </c>
       <c r="T55">
-        <v>1.066069861986495</v>
+        <v>1.089245293768811</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1759464788148126</v>
+        <v>0.1726882106886123</v>
       </c>
       <c r="W55">
-        <v>0.1654699470539856</v>
+        <v>0.1661242072937267</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5498327462962893</v>
+        <v>0.5396506584019135</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1492189675338729</v>
+        <v>0.1507689675338729</v>
       </c>
       <c r="C56">
-        <v>-111.6341403692583</v>
+        <v>-126.0221356051895</v>
       </c>
       <c r="D56">
-        <v>338.9478596307417</v>
+        <v>333.9428643948106</v>
       </c>
       <c r="E56">
-        <v>163.5820000000001</v>
+        <v>172.965</v>
       </c>
       <c r="F56">
-        <v>506.6820000000001</v>
+        <v>516.0650000000001</v>
       </c>
       <c r="G56">
         <v>56.1</v>
@@ -6007,37 +6007,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M56">
-        <v>101.7417456</v>
+        <v>103.625852</v>
       </c>
       <c r="N56">
-        <v>-46.83674560000002</v>
+        <v>-48.72085200000001</v>
       </c>
       <c r="O56">
-        <v>-14.98775859200001</v>
+        <v>-15.59067264</v>
       </c>
       <c r="P56">
-        <v>-31.84898700800002</v>
+        <v>-33.13017936000001</v>
       </c>
       <c r="Q56">
-        <v>-31.37898700800002</v>
+        <v>-32.66017936000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1293736860766533</v>
+        <v>0.1312308791005789</v>
       </c>
       <c r="T56">
-        <v>1.089245293768811</v>
+        <v>1.113450744741451</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1726882106886123</v>
+        <v>0.1695484250397285</v>
       </c>
       <c r="W56">
-        <v>0.1661242072937267</v>
+        <v>0.1667546762520225</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5396506584019135</v>
+        <v>0.5298388282491515</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1507689675338729</v>
+        <v>0.1523189675338729</v>
       </c>
       <c r="C57">
-        <v>-126.0221356051895</v>
+        <v>-140.264471475558</v>
       </c>
       <c r="D57">
-        <v>333.9428643948106</v>
+        <v>329.0835285244421</v>
       </c>
       <c r="E57">
-        <v>172.965</v>
+        <v>182.3480000000001</v>
       </c>
       <c r="F57">
-        <v>516.0650000000001</v>
+        <v>525.4480000000001</v>
       </c>
       <c r="G57">
         <v>56.1</v>
@@ -6089,37 +6089,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M57">
-        <v>103.625852</v>
+        <v>105.5099584</v>
       </c>
       <c r="N57">
-        <v>-48.72085200000001</v>
+        <v>-50.60495840000002</v>
       </c>
       <c r="O57">
-        <v>-15.59067264</v>
+        <v>-16.19358668800001</v>
       </c>
       <c r="P57">
-        <v>-33.13017936000001</v>
+        <v>-34.41137171200002</v>
       </c>
       <c r="Q57">
-        <v>-32.66017936000001</v>
+        <v>-33.94137171200002</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1312308791005789</v>
+        <v>0.1331724899892284</v>
       </c>
       <c r="T57">
-        <v>1.113450744741451</v>
+        <v>1.138756443485575</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1695484250397285</v>
+        <v>0.1665207745925904</v>
       </c>
       <c r="W57">
-        <v>0.1667546762520225</v>
+        <v>0.1673626284618079</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5298388282491515</v>
+        <v>0.5203774206018452</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1523189675338729</v>
+        <v>0.1538689675338729</v>
       </c>
       <c r="C58">
-        <v>-140.264471475558</v>
+        <v>-154.3674154229544</v>
       </c>
       <c r="D58">
-        <v>329.0835285244421</v>
+        <v>324.3635845770457</v>
       </c>
       <c r="E58">
-        <v>182.3480000000001</v>
+        <v>191.7310000000001</v>
       </c>
       <c r="F58">
-        <v>525.4480000000001</v>
+        <v>534.8310000000001</v>
       </c>
       <c r="G58">
         <v>56.1</v>
@@ -6171,37 +6171,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M58">
-        <v>105.5099584</v>
+        <v>107.3940648</v>
       </c>
       <c r="N58">
-        <v>-50.60495840000002</v>
+        <v>-52.48906480000003</v>
       </c>
       <c r="O58">
-        <v>-16.19358668800001</v>
+        <v>-16.79650073600001</v>
       </c>
       <c r="P58">
-        <v>-34.41137171200002</v>
+        <v>-35.69256406400002</v>
       </c>
       <c r="Q58">
-        <v>-33.94137171200002</v>
+        <v>-35.22256406400003</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1331724899892284</v>
+        <v>0.1352044083610709</v>
       </c>
       <c r="T58">
-        <v>1.138756443485575</v>
+        <v>1.165239151473612</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1665207745925904</v>
+        <v>0.1635993574944748</v>
       </c>
       <c r="W58">
-        <v>0.1673626284618079</v>
+        <v>0.1679492490151095</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5203774206018452</v>
+        <v>0.5112479921702338</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1538689675338729</v>
+        <v>0.1554189675338729</v>
       </c>
       <c r="C59">
-        <v>-154.3674154229544</v>
+        <v>-168.3368804062071</v>
       </c>
       <c r="D59">
-        <v>324.3635845770457</v>
+        <v>319.777119593793</v>
       </c>
       <c r="E59">
-        <v>191.7310000000001</v>
+        <v>201.114</v>
       </c>
       <c r="F59">
-        <v>534.8310000000001</v>
+        <v>544.2140000000001</v>
       </c>
       <c r="G59">
         <v>56.1</v>
@@ -6253,37 +6253,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M59">
-        <v>107.3940648</v>
+        <v>109.2781712</v>
       </c>
       <c r="N59">
-        <v>-52.48906480000003</v>
+        <v>-54.37317120000002</v>
       </c>
       <c r="O59">
-        <v>-16.79650073600001</v>
+        <v>-17.39941478400001</v>
       </c>
       <c r="P59">
-        <v>-35.69256406400002</v>
+        <v>-36.97375641600001</v>
       </c>
       <c r="Q59">
-        <v>-35.22256406400003</v>
+        <v>-36.50375641600002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1352044083610709</v>
+        <v>0.1373330847506203</v>
       </c>
       <c r="T59">
-        <v>1.165239151473612</v>
+        <v>1.192982940794412</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1635993574944748</v>
+        <v>0.1607786789169839</v>
       </c>
       <c r="W59">
-        <v>0.1679492490151095</v>
+        <v>0.1685156412734697</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5112479921702338</v>
+        <v>0.5024333716155747</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1554189675338729</v>
+        <v>0.1782058096850162</v>
       </c>
       <c r="C60">
-        <v>-168.3368804062071</v>
+        <v>-232.7530452277929</v>
       </c>
       <c r="D60">
-        <v>319.777119593793</v>
+        <v>264.7439547722071</v>
       </c>
       <c r="E60">
-        <v>201.114</v>
+        <v>210.497</v>
       </c>
       <c r="F60">
-        <v>544.2140000000001</v>
+        <v>553.597</v>
       </c>
       <c r="G60">
         <v>56.1</v>
@@ -6335,45 +6335,45 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M60">
-        <v>109.2781712</v>
+        <v>130.5381726</v>
       </c>
       <c r="N60">
-        <v>-54.37317120000002</v>
+        <v>-75.63317259999999</v>
       </c>
       <c r="O60">
-        <v>-17.39941478400001</v>
+        <v>-24.202615232</v>
       </c>
       <c r="P60">
-        <v>-36.97375641600001</v>
+        <v>-51.430557368</v>
       </c>
       <c r="Q60">
-        <v>-36.50375641600002</v>
+        <v>-50.960557368</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1373330847506202</v>
+        <v>0.1409969213326922</v>
       </c>
       <c r="T60">
-        <v>1.192982940794412</v>
+        <v>1.24073501374354</v>
       </c>
       <c r="U60">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.1607786789169839</v>
+        <v>0.1345935801770217</v>
       </c>
       <c r="W60">
-        <v>0.1685156412734697</v>
+        <v>0.2040628337942583</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.5024333716155747</v>
+        <v>0.4206049380531929</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1782058096850162</v>
+        <v>0.1801058096850162</v>
       </c>
       <c r="C61">
-        <v>-232.7530452277929</v>
+        <v>-245.8813300762064</v>
       </c>
       <c r="D61">
-        <v>264.7439547722071</v>
+        <v>260.9986699237936</v>
       </c>
       <c r="E61">
-        <v>210.497</v>
+        <v>219.88</v>
       </c>
       <c r="F61">
-        <v>553.597</v>
+        <v>562.98</v>
       </c>
       <c r="G61">
         <v>56.1</v>
@@ -6417,37 +6417,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M61">
-        <v>130.5381726</v>
+        <v>132.750684</v>
       </c>
       <c r="N61">
-        <v>-75.63317259999999</v>
+        <v>-77.84568400000001</v>
       </c>
       <c r="O61">
-        <v>-24.202615232</v>
+        <v>-24.91061888</v>
       </c>
       <c r="P61">
-        <v>-51.430557368</v>
+        <v>-52.93506512</v>
       </c>
       <c r="Q61">
-        <v>-50.960557368</v>
+        <v>-52.46506512000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1409969213326922</v>
+        <v>0.1433768443660096</v>
       </c>
       <c r="T61">
-        <v>1.24073501374354</v>
+        <v>1.271753389087129</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.1345935801770217</v>
+        <v>0.132350353840738</v>
       </c>
       <c r="W61">
-        <v>0.2040628337942583</v>
+        <v>0.204591786564354</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.4206049380531929</v>
+        <v>0.4135948557523064</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1801058096850162</v>
+        <v>0.1820058096850162</v>
       </c>
       <c r="C62">
-        <v>-245.8813300762064</v>
+        <v>-258.9051253844389</v>
       </c>
       <c r="D62">
-        <v>260.9986699237936</v>
+        <v>257.3578746155612</v>
       </c>
       <c r="E62">
-        <v>219.88</v>
+        <v>229.263</v>
       </c>
       <c r="F62">
-        <v>562.98</v>
+        <v>572.3630000000001</v>
       </c>
       <c r="G62">
         <v>56.1</v>
@@ -6499,37 +6499,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M62">
-        <v>132.750684</v>
+        <v>134.9631954</v>
       </c>
       <c r="N62">
-        <v>-77.84568400000001</v>
+        <v>-80.05819540000002</v>
       </c>
       <c r="O62">
-        <v>-24.91061888</v>
+        <v>-25.61862252800001</v>
       </c>
       <c r="P62">
-        <v>-52.93506512</v>
+        <v>-54.43957287200001</v>
       </c>
       <c r="Q62">
-        <v>-52.46506512000001</v>
+        <v>-53.96957287200001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1433768443660096</v>
+        <v>0.1458788147343688</v>
       </c>
       <c r="T62">
-        <v>1.271753389087129</v>
+        <v>1.304362450345774</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.132350353840738</v>
+        <v>0.1301806759089226</v>
       </c>
       <c r="W62">
-        <v>0.204591786564354</v>
+        <v>0.2051033966206761</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.4135948557523064</v>
+        <v>0.4068146122153832</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1820058096850162</v>
+        <v>0.1839058096850162</v>
       </c>
       <c r="C63">
-        <v>-258.9051253844389</v>
+        <v>-271.828743718199</v>
       </c>
       <c r="D63">
-        <v>257.3578746155612</v>
+        <v>253.8172562818011</v>
       </c>
       <c r="E63">
-        <v>229.263</v>
+        <v>238.6460000000001</v>
       </c>
       <c r="F63">
-        <v>572.3630000000001</v>
+        <v>581.7460000000001</v>
       </c>
       <c r="G63">
         <v>56.1</v>
@@ -6581,37 +6581,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M63">
-        <v>134.9631954</v>
+        <v>137.1757068</v>
       </c>
       <c r="N63">
-        <v>-80.05819540000002</v>
+        <v>-82.27070680000003</v>
       </c>
       <c r="O63">
-        <v>-25.61862252800001</v>
+        <v>-26.32662617600001</v>
       </c>
       <c r="P63">
-        <v>-54.43957287200001</v>
+        <v>-55.94408062400002</v>
       </c>
       <c r="Q63">
-        <v>-53.96957287200001</v>
+        <v>-55.47408062400002</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1458788147343688</v>
+        <v>0.1485124677536943</v>
       </c>
       <c r="T63">
-        <v>1.304362450345774</v>
+        <v>1.338687777986452</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.1301806759089226</v>
+        <v>0.128080987587811</v>
       </c>
       <c r="W63">
-        <v>0.2051033966206761</v>
+        <v>0.2055985031267942</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4068146122153832</v>
+        <v>0.4002530862119092</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1839058096850162</v>
+        <v>0.1858058096850162</v>
       </c>
       <c r="C64">
-        <v>-271.828743718199</v>
+        <v>-284.6562635422005</v>
       </c>
       <c r="D64">
-        <v>253.8172562818011</v>
+        <v>250.3727364577995</v>
       </c>
       <c r="E64">
-        <v>238.6460000000001</v>
+        <v>248.029</v>
       </c>
       <c r="F64">
-        <v>581.7460000000001</v>
+        <v>591.129</v>
       </c>
       <c r="G64">
         <v>56.1</v>
@@ -6663,37 +6663,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M64">
-        <v>137.1757068</v>
+        <v>139.3882182</v>
       </c>
       <c r="N64">
-        <v>-82.27070680000003</v>
+        <v>-84.48321820000001</v>
       </c>
       <c r="O64">
-        <v>-26.32662617600001</v>
+        <v>-27.034629824</v>
       </c>
       <c r="P64">
-        <v>-55.94408062400002</v>
+        <v>-57.448588376</v>
       </c>
       <c r="Q64">
-        <v>-55.47408062400002</v>
+        <v>-56.978588376</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1485124677536943</v>
+        <v>0.151288480395686</v>
       </c>
       <c r="T64">
-        <v>1.338687777986452</v>
+        <v>1.374868528742842</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.128080987587811</v>
+        <v>0.1260479560387981</v>
       </c>
       <c r="W64">
-        <v>0.2055985031267942</v>
+        <v>0.2060778919660514</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4002530862119092</v>
+        <v>0.3938998626212441</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1858058096850162</v>
+        <v>0.1877058096850162</v>
       </c>
       <c r="C65">
-        <v>-284.6562635422005</v>
+        <v>-297.3915448922435</v>
       </c>
       <c r="D65">
-        <v>250.3727364577995</v>
+        <v>247.0204551077565</v>
       </c>
       <c r="E65">
-        <v>248.029</v>
+        <v>257.412</v>
       </c>
       <c r="F65">
-        <v>591.129</v>
+        <v>600.5120000000001</v>
       </c>
       <c r="G65">
         <v>56.1</v>
@@ -6745,37 +6745,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M65">
-        <v>139.3882182</v>
+        <v>141.6007296</v>
       </c>
       <c r="N65">
-        <v>-84.48321820000001</v>
+        <v>-86.69572960000002</v>
       </c>
       <c r="O65">
-        <v>-27.034629824</v>
+        <v>-27.74263347200001</v>
       </c>
       <c r="P65">
-        <v>-57.448588376</v>
+        <v>-58.95309612800001</v>
       </c>
       <c r="Q65">
-        <v>-56.978588376</v>
+        <v>-58.48309612800001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.151288480395686</v>
+        <v>0.1542187159622329</v>
       </c>
       <c r="T65">
-        <v>1.374868528742842</v>
+        <v>1.413059321207921</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.1260479560387981</v>
+        <v>0.1240784567256919</v>
       </c>
       <c r="W65">
-        <v>0.2060778919660514</v>
+        <v>0.2065422999040819</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3938998626212441</v>
+        <v>0.3877451772677871</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1877058096850162</v>
+        <v>0.1896058096850162</v>
       </c>
       <c r="C66">
-        <v>-297.3915448922435</v>
+        <v>-310.0382438049144</v>
       </c>
       <c r="D66">
-        <v>247.0204551077565</v>
+        <v>243.7567561950857</v>
       </c>
       <c r="E66">
-        <v>257.412</v>
+        <v>266.7950000000001</v>
       </c>
       <c r="F66">
-        <v>600.5120000000001</v>
+        <v>609.8950000000001</v>
       </c>
       <c r="G66">
         <v>56.1</v>
@@ -6827,37 +6827,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M66">
-        <v>141.6007296</v>
+        <v>143.813241</v>
       </c>
       <c r="N66">
-        <v>-86.69572960000002</v>
+        <v>-88.90824100000003</v>
       </c>
       <c r="O66">
-        <v>-27.74263347200001</v>
+        <v>-28.45063712000001</v>
       </c>
       <c r="P66">
-        <v>-58.95309612800001</v>
+        <v>-60.45760388000002</v>
       </c>
       <c r="Q66">
-        <v>-58.48309612800001</v>
+        <v>-59.98760388000002</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1542187159622329</v>
+        <v>0.1573163935611538</v>
       </c>
       <c r="T66">
-        <v>1.413059321207921</v>
+        <v>1.453432444671005</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.1240784567256919</v>
+        <v>0.1221695573914504</v>
       </c>
       <c r="W66">
-        <v>0.2065422999040819</v>
+        <v>0.206992418367096</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3877451772677871</v>
+        <v>0.3817798668482827</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1896058096850162</v>
+        <v>0.1915058096850162</v>
       </c>
       <c r="C67">
-        <v>-310.0382438049144</v>
+        <v>-322.5998256183086</v>
       </c>
       <c r="D67">
-        <v>243.7567561950857</v>
+        <v>240.5781743816915</v>
       </c>
       <c r="E67">
-        <v>266.7950000000001</v>
+        <v>276.178</v>
       </c>
       <c r="F67">
-        <v>609.8950000000001</v>
+        <v>619.278</v>
       </c>
       <c r="G67">
         <v>56.1</v>
@@ -6909,37 +6909,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M67">
-        <v>143.813241</v>
+        <v>146.0257524</v>
       </c>
       <c r="N67">
-        <v>-88.90824100000003</v>
+        <v>-91.12075240000001</v>
       </c>
       <c r="O67">
-        <v>-28.45063712000001</v>
+        <v>-29.15864076800001</v>
       </c>
       <c r="P67">
-        <v>-60.45760388000002</v>
+        <v>-61.96211163200001</v>
       </c>
       <c r="Q67">
-        <v>-59.98760388000002</v>
+        <v>-61.49211163200001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1573163935611538</v>
+        <v>0.160596287489423</v>
       </c>
       <c r="T67">
-        <v>1.453432444671005</v>
+        <v>1.496180457749564</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.1221695573914504</v>
+        <v>0.12031850349158</v>
       </c>
       <c r="W67">
-        <v>0.206992418367096</v>
+        <v>0.2074288968766854</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3817798668482827</v>
+        <v>0.3759953234111876</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1915058096850162</v>
+        <v>0.1934058096850163</v>
       </c>
       <c r="C68">
-        <v>-322.5998256183086</v>
+        <v>-335.0795772455015</v>
       </c>
       <c r="D68">
-        <v>240.5781743816915</v>
+        <v>237.4814227544985</v>
       </c>
       <c r="E68">
-        <v>276.178</v>
+        <v>285.561</v>
       </c>
       <c r="F68">
-        <v>619.278</v>
+        <v>628.6610000000001</v>
       </c>
       <c r="G68">
         <v>56.1</v>
@@ -6991,37 +6991,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M68">
-        <v>146.0257524</v>
+        <v>148.2382638</v>
       </c>
       <c r="N68">
-        <v>-91.12075240000001</v>
+        <v>-93.33326380000003</v>
       </c>
       <c r="O68">
-        <v>-29.15864076800001</v>
+        <v>-29.86664441600001</v>
       </c>
       <c r="P68">
-        <v>-61.96211163200001</v>
+        <v>-63.46661938400001</v>
       </c>
       <c r="Q68">
-        <v>-61.49211163200001</v>
+        <v>-62.99661938400001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.160596287489423</v>
+        <v>0.1640749628678904</v>
       </c>
       <c r="T68">
-        <v>1.496180457749564</v>
+        <v>1.541519259499551</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.12031850349158</v>
+        <v>0.1185227049320042</v>
       </c>
       <c r="W68">
-        <v>0.2074288968766854</v>
+        <v>0.2078523461770334</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3759953234111876</v>
+        <v>0.3703834529125131</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1934058096850163</v>
+        <v>0.1953058096850162</v>
       </c>
       <c r="C69">
-        <v>-335.0795772455015</v>
+        <v>-347.4806185121532</v>
       </c>
       <c r="D69">
-        <v>237.4814227544985</v>
+        <v>234.4633814878469</v>
       </c>
       <c r="E69">
-        <v>285.561</v>
+        <v>294.9440000000001</v>
       </c>
       <c r="F69">
-        <v>628.6610000000001</v>
+        <v>638.0440000000001</v>
       </c>
       <c r="G69">
         <v>56.1</v>
@@ -7073,37 +7073,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M69">
-        <v>148.2382638</v>
+        <v>150.4507752</v>
       </c>
       <c r="N69">
-        <v>-93.33326380000003</v>
+        <v>-95.54577520000004</v>
       </c>
       <c r="O69">
-        <v>-29.86664441600001</v>
+        <v>-30.57464806400001</v>
       </c>
       <c r="P69">
-        <v>-63.46661938400001</v>
+        <v>-64.97112713600002</v>
       </c>
       <c r="Q69">
-        <v>-62.99661938400001</v>
+        <v>-64.50112713600002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1640749628678904</v>
+        <v>0.1677710554575119</v>
       </c>
       <c r="T69">
-        <v>1.541519259499551</v>
+        <v>1.589691736358912</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.1185227049320042</v>
+        <v>0.1167797239771217</v>
       </c>
       <c r="W69">
-        <v>0.2078523461770334</v>
+        <v>0.2082633410861947</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3703834529125131</v>
+        <v>0.3649366374285055</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1953058096850162</v>
+        <v>0.1972058096850162</v>
       </c>
       <c r="C70">
-        <v>-347.4806185121532</v>
+        <v>-359.8059126404544</v>
       </c>
       <c r="D70">
-        <v>234.4633814878469</v>
+        <v>231.5210873595457</v>
       </c>
       <c r="E70">
-        <v>294.9440000000001</v>
+        <v>304.3270000000001</v>
       </c>
       <c r="F70">
-        <v>638.0440000000001</v>
+        <v>647.4270000000001</v>
       </c>
       <c r="G70">
         <v>56.1</v>
@@ -7155,37 +7155,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M70">
-        <v>150.4507752</v>
+        <v>152.6632866</v>
       </c>
       <c r="N70">
-        <v>-95.54577520000004</v>
+        <v>-97.75828660000005</v>
       </c>
       <c r="O70">
-        <v>-30.57464806400001</v>
+        <v>-31.28265171200002</v>
       </c>
       <c r="P70">
-        <v>-64.97112713600002</v>
+        <v>-66.47563488800003</v>
       </c>
       <c r="Q70">
-        <v>-64.50112713600002</v>
+        <v>-66.00563488800003</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1677710554575119</v>
+        <v>0.1717056056335608</v>
       </c>
       <c r="T70">
-        <v>1.589691736358912</v>
+        <v>1.640972114951135</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.1167797239771217</v>
+        <v>0.1150872642093374</v>
       </c>
       <c r="W70">
-        <v>0.2082633410861947</v>
+        <v>0.2086624230994382</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3649366374285055</v>
+        <v>0.3596477006541793</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1972058096850162</v>
+        <v>0.1991058096850162</v>
       </c>
       <c r="C71">
-        <v>-359.8059126404544</v>
+        <v>-372.0582759534752</v>
       </c>
       <c r="D71">
-        <v>231.5210873595457</v>
+        <v>228.6517240465249</v>
       </c>
       <c r="E71">
-        <v>304.3270000000001</v>
+        <v>313.71</v>
       </c>
       <c r="F71">
-        <v>647.4270000000001</v>
+        <v>656.8100000000001</v>
       </c>
       <c r="G71">
         <v>56.1</v>
@@ -7237,37 +7237,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M71">
-        <v>152.6632866</v>
+        <v>154.875798</v>
       </c>
       <c r="N71">
-        <v>-97.75828660000005</v>
+        <v>-99.97079800000003</v>
       </c>
       <c r="O71">
-        <v>-31.28265171200002</v>
+        <v>-31.99065536000001</v>
       </c>
       <c r="P71">
-        <v>-66.47563488800003</v>
+        <v>-67.98014264000003</v>
       </c>
       <c r="Q71">
-        <v>-66.00563488800003</v>
+        <v>-67.51014264000003</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1717056056335608</v>
+        <v>0.1759024591546794</v>
       </c>
       <c r="T71">
-        <v>1.640972114951135</v>
+        <v>1.695671185449506</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.1150872642093374</v>
+        <v>0.1134431604349183</v>
       </c>
       <c r="W71">
-        <v>0.2086624230994382</v>
+        <v>0.2090501027694463</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3596477006541793</v>
+        <v>0.3545098763591197</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1991058096850162</v>
+        <v>0.2010058096850162</v>
       </c>
       <c r="C72">
-        <v>-372.0582759534752</v>
+        <v>-384.2403868667205</v>
       </c>
       <c r="D72">
-        <v>228.6517240465249</v>
+        <v>225.8526131332796</v>
       </c>
       <c r="E72">
-        <v>313.71</v>
+        <v>323.0930000000001</v>
       </c>
       <c r="F72">
-        <v>656.8100000000001</v>
+        <v>666.1930000000001</v>
       </c>
       <c r="G72">
         <v>56.1</v>
@@ -7319,37 +7319,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M72">
-        <v>154.875798</v>
+        <v>157.0883094</v>
       </c>
       <c r="N72">
-        <v>-99.97079800000003</v>
+        <v>-102.1833094</v>
       </c>
       <c r="O72">
-        <v>-31.99065536000001</v>
+        <v>-32.69865900800001</v>
       </c>
       <c r="P72">
-        <v>-67.98014264000003</v>
+        <v>-69.48465039200002</v>
       </c>
       <c r="Q72">
-        <v>-67.51014264000003</v>
+        <v>-69.01465039200002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1759024591546794</v>
+        <v>0.1803887508496684</v>
       </c>
       <c r="T72">
-        <v>1.695671185449506</v>
+        <v>1.75414260563742</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.1134431604349183</v>
+        <v>0.1118453694428772</v>
       </c>
       <c r="W72">
-        <v>0.2090501027694463</v>
+        <v>0.2094268618853696</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3545098763591197</v>
+        <v>0.3495167795089912</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2010058096850162</v>
+        <v>0.2029058096850162</v>
       </c>
       <c r="C73">
-        <v>-384.2403868667203</v>
+        <v>-396.3547942272348</v>
       </c>
       <c r="D73">
-        <v>225.8526131332796</v>
+        <v>223.1212057727652</v>
       </c>
       <c r="E73">
-        <v>323.093</v>
+        <v>332.476</v>
       </c>
       <c r="F73">
-        <v>666.193</v>
+        <v>675.576</v>
       </c>
       <c r="G73">
         <v>56.1</v>
@@ -7401,37 +7401,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M73">
-        <v>157.0883094</v>
+        <v>159.3008208</v>
       </c>
       <c r="N73">
-        <v>-102.1833094</v>
+        <v>-104.3958208</v>
       </c>
       <c r="O73">
-        <v>-32.69865900800001</v>
+        <v>-33.40666265600001</v>
       </c>
       <c r="P73">
-        <v>-69.48465039200001</v>
+        <v>-70.98915814400002</v>
       </c>
       <c r="Q73">
-        <v>-69.01465039200001</v>
+        <v>-70.51915814400002</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1803887508496684</v>
+        <v>0.1851954919514422</v>
       </c>
       <c r="T73">
-        <v>1.75414260563742</v>
+        <v>1.816790555838756</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.1118453694428772</v>
+        <v>0.1102919615339483</v>
       </c>
       <c r="W73">
-        <v>0.2094268618853696</v>
+        <v>0.209793155470295</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3495167795089913</v>
+        <v>0.3446623797935886</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2029058096850162</v>
+        <v>0.2048058096850162</v>
       </c>
       <c r="C74">
-        <v>-396.3547942272348</v>
+        <v>-408.4039250548319</v>
       </c>
       <c r="D74">
-        <v>223.1212057727652</v>
+        <v>220.4550749451681</v>
       </c>
       <c r="E74">
-        <v>332.476</v>
+        <v>341.859</v>
       </c>
       <c r="F74">
-        <v>675.576</v>
+        <v>684.9590000000001</v>
       </c>
       <c r="G74">
         <v>56.1</v>
@@ -7483,37 +7483,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M74">
-        <v>159.3008208</v>
+        <v>161.5133322</v>
       </c>
       <c r="N74">
-        <v>-104.3958208</v>
+        <v>-106.6083322</v>
       </c>
       <c r="O74">
-        <v>-33.40666265600001</v>
+        <v>-34.114666304</v>
       </c>
       <c r="P74">
-        <v>-70.98915814400002</v>
+        <v>-72.49366589600001</v>
       </c>
       <c r="Q74">
-        <v>-70.51915814400002</v>
+        <v>-72.02366589600001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1851954919514422</v>
+        <v>0.1903582879496438</v>
       </c>
       <c r="T74">
-        <v>1.816790555838756</v>
+        <v>1.884079094943895</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.1102919615339483</v>
+        <v>0.1087811127458121</v>
       </c>
       <c r="W74">
-        <v>0.209793155470295</v>
+        <v>0.2101494136145375</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3446623797935886</v>
+        <v>0.3399409773306628</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2048058096850162</v>
+        <v>0.2067058096850162</v>
       </c>
       <c r="C75">
-        <v>-408.4039250548319</v>
+        <v>-420.3900917348653</v>
       </c>
       <c r="D75">
-        <v>220.4550749451681</v>
+        <v>217.8519082651348</v>
       </c>
       <c r="E75">
-        <v>341.859</v>
+        <v>351.2420000000001</v>
       </c>
       <c r="F75">
-        <v>684.9590000000001</v>
+        <v>694.3420000000001</v>
       </c>
       <c r="G75">
         <v>56.1</v>
@@ -7565,37 +7565,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M75">
-        <v>161.5133322</v>
+        <v>163.7258436</v>
       </c>
       <c r="N75">
-        <v>-106.6083322</v>
+        <v>-108.8208436</v>
       </c>
       <c r="O75">
-        <v>-34.114666304</v>
+        <v>-34.82266995200001</v>
       </c>
       <c r="P75">
-        <v>-72.49366589600001</v>
+        <v>-73.99817364800001</v>
       </c>
       <c r="Q75">
-        <v>-72.02366589600001</v>
+        <v>-73.52817364800001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1903582879496438</v>
+        <v>0.1959182221015532</v>
       </c>
       <c r="T75">
-        <v>1.884079094943895</v>
+        <v>1.95654367551866</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.1087811127458121</v>
+        <v>0.1073110977087065</v>
       </c>
       <c r="W75">
-        <v>0.2101494136145375</v>
+        <v>0.210496043160287</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3399409773306628</v>
+        <v>0.3353471803397078</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2067058096850162</v>
+        <v>0.2086058096850162</v>
       </c>
       <c r="C76">
-        <v>-420.3900917348653</v>
+        <v>-432.3154987073472</v>
       </c>
       <c r="D76">
-        <v>217.8519082651348</v>
+        <v>215.3095012926529</v>
       </c>
       <c r="E76">
-        <v>351.2420000000001</v>
+        <v>360.625</v>
       </c>
       <c r="F76">
-        <v>694.3420000000001</v>
+        <v>703.725</v>
       </c>
       <c r="G76">
         <v>56.1</v>
@@ -7647,37 +7647,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M76">
-        <v>163.7258436</v>
+        <v>165.938355</v>
       </c>
       <c r="N76">
-        <v>-108.8208436</v>
+        <v>-111.033355</v>
       </c>
       <c r="O76">
-        <v>-34.82266995200001</v>
+        <v>-35.5306736</v>
       </c>
       <c r="P76">
-        <v>-73.99817364800001</v>
+        <v>-75.5026814</v>
       </c>
       <c r="Q76">
-        <v>-73.52817364800001</v>
+        <v>-75.0326814</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1959182221015532</v>
+        <v>0.2019229509856153</v>
       </c>
       <c r="T76">
-        <v>1.95654367551866</v>
+        <v>2.034805422539407</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.1073110977087065</v>
+        <v>0.1058802830725904</v>
       </c>
       <c r="W76">
-        <v>0.210496043160287</v>
+        <v>0.2108334292514832</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3353471803397078</v>
+        <v>0.330875884601845</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2086058096850162</v>
+        <v>0.2105058096850162</v>
       </c>
       <c r="C77">
-        <v>-432.3154987073472</v>
+        <v>-444.1822486930847</v>
       </c>
       <c r="D77">
-        <v>215.3095012926529</v>
+        <v>212.8257513069154</v>
       </c>
       <c r="E77">
-        <v>360.625</v>
+        <v>370.008</v>
       </c>
       <c r="F77">
-        <v>703.725</v>
+        <v>713.1080000000001</v>
       </c>
       <c r="G77">
         <v>56.1</v>
@@ -7729,37 +7729,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M77">
-        <v>165.938355</v>
+        <v>168.1508664</v>
       </c>
       <c r="N77">
-        <v>-111.033355</v>
+        <v>-113.2458664</v>
       </c>
       <c r="O77">
-        <v>-35.5306736</v>
+        <v>-36.238677248</v>
       </c>
       <c r="P77">
-        <v>-75.5026814</v>
+        <v>-77.00718915200001</v>
       </c>
       <c r="Q77">
-        <v>-75.0326814</v>
+        <v>-76.53718915200001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2019229509856153</v>
+        <v>0.2084280739433493</v>
       </c>
       <c r="T77">
-        <v>2.034805422539407</v>
+        <v>2.119588981811882</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1058802830725904</v>
+        <v>0.1044871214532142</v>
       </c>
       <c r="W77">
-        <v>0.2108334292514832</v>
+        <v>0.2111619367613321</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.330875884601845</v>
+        <v>0.3265222545412945</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2105058096850162</v>
+        <v>0.2124058096850162</v>
       </c>
       <c r="C78">
-        <v>-444.1822486930847</v>
+        <v>-455.9923484937918</v>
       </c>
       <c r="D78">
-        <v>212.8257513069154</v>
+        <v>210.3986515062083</v>
       </c>
       <c r="E78">
-        <v>370.008</v>
+        <v>379.3910000000001</v>
       </c>
       <c r="F78">
-        <v>713.1080000000001</v>
+        <v>722.4910000000001</v>
       </c>
       <c r="G78">
         <v>56.1</v>
@@ -7811,37 +7811,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M78">
-        <v>168.1508664</v>
+        <v>170.3633778</v>
       </c>
       <c r="N78">
-        <v>-113.2458664</v>
+        <v>-115.4583778</v>
       </c>
       <c r="O78">
-        <v>-36.238677248</v>
+        <v>-36.94668089600001</v>
       </c>
       <c r="P78">
-        <v>-77.00718915200001</v>
+        <v>-78.51169690400002</v>
       </c>
       <c r="Q78">
-        <v>-76.53718915200001</v>
+        <v>-78.04169690400002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2084280739433493</v>
+        <v>0.2154988597669731</v>
       </c>
       <c r="T78">
-        <v>2.119588981811882</v>
+        <v>2.211745024499355</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1044871214532142</v>
+        <v>0.1031301458499257</v>
       </c>
       <c r="W78">
-        <v>0.2111619367613321</v>
+        <v>0.2114819116085875</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3265222545412945</v>
+        <v>0.3222817057810179</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2124058096850162</v>
+        <v>0.2143058096850162</v>
       </c>
       <c r="C79">
-        <v>-455.9923484937918</v>
+        <v>-467.7477143998044</v>
       </c>
       <c r="D79">
-        <v>210.3986515062083</v>
+        <v>208.0262856001956</v>
       </c>
       <c r="E79">
-        <v>379.3910000000001</v>
+        <v>388.774</v>
       </c>
       <c r="F79">
-        <v>722.4910000000001</v>
+        <v>731.874</v>
       </c>
       <c r="G79">
         <v>56.1</v>
@@ -7893,37 +7893,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M79">
-        <v>170.3633778</v>
+        <v>172.5758892</v>
       </c>
       <c r="N79">
-        <v>-115.4583778</v>
+        <v>-117.6708892</v>
       </c>
       <c r="O79">
-        <v>-36.94668089600001</v>
+        <v>-37.65468454400001</v>
       </c>
       <c r="P79">
-        <v>-78.51169690400002</v>
+        <v>-80.016204656</v>
       </c>
       <c r="Q79">
-        <v>-78.04169690400002</v>
+        <v>-79.546204656</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2154988597669731</v>
+        <v>0.2232124443018356</v>
       </c>
       <c r="T79">
-        <v>2.211745024499355</v>
+        <v>2.312278889249326</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1031301458499257</v>
+        <v>0.1018079644928754</v>
       </c>
       <c r="W79">
-        <v>0.2114819116085875</v>
+        <v>0.21179368197258</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3222817057810179</v>
+        <v>0.3181498890402357</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2143058096850162</v>
+        <v>0.2162058096850162</v>
       </c>
       <c r="C80">
-        <v>-467.7477143998044</v>
+        <v>-479.4501772360245</v>
       </c>
       <c r="D80">
-        <v>208.0262856001956</v>
+        <v>205.7068227639756</v>
       </c>
       <c r="E80">
-        <v>388.774</v>
+        <v>398.157</v>
       </c>
       <c r="F80">
-        <v>731.874</v>
+        <v>741.2570000000001</v>
       </c>
       <c r="G80">
         <v>56.1</v>
@@ -7975,37 +7975,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M80">
-        <v>172.5758892</v>
+        <v>174.7884006</v>
       </c>
       <c r="N80">
-        <v>-117.6708892</v>
+        <v>-119.8834006</v>
       </c>
       <c r="O80">
-        <v>-37.65468454400001</v>
+        <v>-38.36268819200001</v>
       </c>
       <c r="P80">
-        <v>-80.016204656</v>
+        <v>-81.52071240800001</v>
       </c>
       <c r="Q80">
-        <v>-79.546204656</v>
+        <v>-81.05071240800001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2232124443018356</v>
+        <v>0.2316606559352564</v>
       </c>
       <c r="T80">
-        <v>2.312278889249326</v>
+        <v>2.422387407785008</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1018079644928754</v>
+        <v>0.1005192560815732</v>
       </c>
       <c r="W80">
-        <v>0.21179368197258</v>
+        <v>0.2120975594159651</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3181498890402357</v>
+        <v>0.3141226752549162</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2162058096850162</v>
+        <v>0.2181058096850162</v>
       </c>
       <c r="C81">
-        <v>-479.4501772360245</v>
+        <v>-491.1014870740157</v>
       </c>
       <c r="D81">
-        <v>205.7068227639756</v>
+        <v>203.4385129259844</v>
       </c>
       <c r="E81">
-        <v>398.157</v>
+        <v>407.5400000000001</v>
       </c>
       <c r="F81">
-        <v>741.2570000000001</v>
+        <v>750.6400000000001</v>
       </c>
       <c r="G81">
         <v>56.1</v>
@@ -8057,37 +8057,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M81">
-        <v>174.7884006</v>
+        <v>177.000912</v>
       </c>
       <c r="N81">
-        <v>-119.8834006</v>
+        <v>-122.095912</v>
       </c>
       <c r="O81">
-        <v>-38.36268819200001</v>
+        <v>-39.07069184000001</v>
       </c>
       <c r="P81">
-        <v>-81.52071240800001</v>
+        <v>-83.02522016000002</v>
       </c>
       <c r="Q81">
-        <v>-81.05071240800001</v>
+        <v>-82.55522016000002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2316606559352564</v>
+        <v>0.2409536887320192</v>
       </c>
       <c r="T81">
-        <v>2.422387407785008</v>
+        <v>2.54350677817426</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1005192560815732</v>
+        <v>0.09926276538055349</v>
       </c>
       <c r="W81">
-        <v>0.2120975594159651</v>
+        <v>0.2123938399232655</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3141226752549162</v>
+        <v>0.3101961418142297</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2181058096850162</v>
+        <v>0.2200058096850162</v>
       </c>
       <c r="C82">
-        <v>-491.1014870740157</v>
+        <v>-502.7033176357418</v>
       </c>
       <c r="D82">
-        <v>203.4385129259844</v>
+        <v>201.2196823642583</v>
       </c>
       <c r="E82">
-        <v>407.5400000000001</v>
+        <v>416.9230000000001</v>
       </c>
       <c r="F82">
-        <v>750.6400000000001</v>
+        <v>760.0230000000001</v>
       </c>
       <c r="G82">
         <v>56.1</v>
@@ -8139,37 +8139,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M82">
-        <v>177.000912</v>
+        <v>179.2134234</v>
       </c>
       <c r="N82">
-        <v>-122.095912</v>
+        <v>-124.3084234</v>
       </c>
       <c r="O82">
-        <v>-39.07069184000001</v>
+        <v>-39.77869548800001</v>
       </c>
       <c r="P82">
-        <v>-83.02522016000002</v>
+        <v>-84.52972791200003</v>
       </c>
       <c r="Q82">
-        <v>-82.55522016000002</v>
+        <v>-84.05972791200003</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2409536887320192</v>
+        <v>0.2512249355073886</v>
       </c>
       <c r="T82">
-        <v>2.54350677817426</v>
+        <v>2.677375555972905</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.09926276538055349</v>
+        <v>0.09803729914128739</v>
       </c>
       <c r="W82">
-        <v>0.2123938399232655</v>
+        <v>0.2126828048624844</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3101961418142297</v>
+        <v>0.3063665598165232</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2200058096850162</v>
+        <v>0.2219058096850162</v>
       </c>
       <c r="C83">
-        <v>-502.7033176357418</v>
+        <v>-514.257270412234</v>
       </c>
       <c r="D83">
-        <v>201.2196823642583</v>
+        <v>199.0487295877661</v>
       </c>
       <c r="E83">
-        <v>416.9230000000001</v>
+        <v>426.306</v>
       </c>
       <c r="F83">
-        <v>760.0230000000001</v>
+        <v>769.4060000000001</v>
       </c>
       <c r="G83">
         <v>56.1</v>
@@ -8221,37 +8221,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M83">
-        <v>179.2134234</v>
+        <v>181.4259348</v>
       </c>
       <c r="N83">
-        <v>-124.3084234</v>
+        <v>-126.5209348</v>
       </c>
       <c r="O83">
-        <v>-39.77869548800001</v>
+        <v>-40.48669913600001</v>
       </c>
       <c r="P83">
-        <v>-84.52972791200003</v>
+        <v>-86.03423566400002</v>
       </c>
       <c r="Q83">
-        <v>-84.05972791200003</v>
+        <v>-85.56423566400002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2512249355073886</v>
+        <v>0.2626374319244658</v>
       </c>
       <c r="T83">
-        <v>2.677375555972905</v>
+        <v>2.826118642415843</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.09803729914128739</v>
+        <v>0.09684172232249122</v>
       </c>
       <c r="W83">
-        <v>0.2126828048624844</v>
+        <v>0.2129647218763566</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3063665598165232</v>
+        <v>0.302630382257785</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2219058096850162</v>
+        <v>0.2238058096850162</v>
       </c>
       <c r="C84">
-        <v>-514.257270412234</v>
+        <v>-525.7648785184862</v>
       </c>
       <c r="D84">
-        <v>199.0487295877661</v>
+        <v>196.924121481514</v>
       </c>
       <c r="E84">
-        <v>426.306</v>
+        <v>435.6890000000001</v>
       </c>
       <c r="F84">
-        <v>769.4060000000001</v>
+        <v>778.7890000000001</v>
       </c>
       <c r="G84">
         <v>56.1</v>
@@ -8303,37 +8303,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M84">
-        <v>181.4259348</v>
+        <v>183.6384462</v>
       </c>
       <c r="N84">
-        <v>-126.5209348</v>
+        <v>-128.7334462</v>
       </c>
       <c r="O84">
-        <v>-40.48669913600001</v>
+        <v>-41.19470278400001</v>
       </c>
       <c r="P84">
-        <v>-86.03423566400002</v>
+        <v>-87.53874341600002</v>
       </c>
       <c r="Q84">
-        <v>-85.56423566400002</v>
+        <v>-87.06874341600002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2626374319244658</v>
+        <v>0.2753925749788461</v>
       </c>
       <c r="T84">
-        <v>2.826118642415843</v>
+        <v>2.992360915499129</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.09684172232249122</v>
+        <v>0.09567495458366601</v>
       </c>
       <c r="W84">
-        <v>0.2129647218763566</v>
+        <v>0.2132398457091716</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.302630382257785</v>
+        <v>0.2989842330739564</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2238058096850162</v>
+        <v>0.2257058096850162</v>
       </c>
       <c r="C85">
-        <v>-525.7648785184862</v>
+        <v>-537.2276103040798</v>
       </c>
       <c r="D85">
-        <v>196.924121481514</v>
+        <v>194.8443896959204</v>
       </c>
       <c r="E85">
-        <v>435.6890000000001</v>
+        <v>445.0720000000001</v>
       </c>
       <c r="F85">
-        <v>778.7890000000001</v>
+        <v>788.1720000000001</v>
       </c>
       <c r="G85">
         <v>56.1</v>
@@ -8385,37 +8385,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M85">
-        <v>183.6384462</v>
+        <v>185.8509576</v>
       </c>
       <c r="N85">
-        <v>-128.7334462</v>
+        <v>-130.9459576</v>
       </c>
       <c r="O85">
-        <v>-41.19470278400001</v>
+        <v>-41.90270643200002</v>
       </c>
       <c r="P85">
-        <v>-87.53874341600002</v>
+        <v>-89.04325116800003</v>
       </c>
       <c r="Q85">
-        <v>-87.06874341600002</v>
+        <v>-88.57325116800003</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2753925749788461</v>
+        <v>0.289742110915024</v>
       </c>
       <c r="T85">
-        <v>2.992360915499129</v>
+        <v>3.179383472717825</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.09567495458366601</v>
+        <v>0.09453596702909856</v>
       </c>
       <c r="W85">
-        <v>0.2132398457091716</v>
+        <v>0.2135084189745386</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2989842330739564</v>
+        <v>0.295424896965933</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2257058096850162</v>
+        <v>0.2276058096850162</v>
       </c>
       <c r="C86">
-        <v>-537.2276103040797</v>
+        <v>-548.646872737407</v>
       </c>
       <c r="D86">
-        <v>194.8443896959204</v>
+        <v>192.808127262593</v>
       </c>
       <c r="E86">
-        <v>445.072</v>
+        <v>454.455</v>
       </c>
       <c r="F86">
-        <v>788.172</v>
+        <v>797.5550000000001</v>
       </c>
       <c r="G86">
         <v>56.1</v>
@@ -8467,37 +8467,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M86">
-        <v>185.8509576</v>
+        <v>188.063469</v>
       </c>
       <c r="N86">
-        <v>-130.9459576</v>
+        <v>-133.158469</v>
       </c>
       <c r="O86">
-        <v>-41.902706432</v>
+        <v>-42.61071008000001</v>
       </c>
       <c r="P86">
-        <v>-89.04325116800001</v>
+        <v>-90.54775892000001</v>
       </c>
       <c r="Q86">
-        <v>-88.57325116800001</v>
+        <v>-90.07775892000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2897421109150239</v>
+        <v>0.3060049183093588</v>
       </c>
       <c r="T86">
-        <v>3.179383472717823</v>
+        <v>3.391342370899011</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.09453596702909858</v>
+        <v>0.09342377918169741</v>
       </c>
       <c r="W86">
-        <v>0.2135084189745386</v>
+        <v>0.2137706728689558</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2954248969659331</v>
+        <v>0.2919493099428044</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2276058096850162</v>
+        <v>0.2295058096850162</v>
       </c>
       <c r="C87">
-        <v>-548.646872737407</v>
+        <v>-560.0240145798836</v>
       </c>
       <c r="D87">
-        <v>192.808127262593</v>
+        <v>190.8139854201166</v>
       </c>
       <c r="E87">
-        <v>454.455</v>
+        <v>463.8380000000001</v>
       </c>
       <c r="F87">
-        <v>797.5550000000001</v>
+        <v>806.9380000000001</v>
       </c>
       <c r="G87">
         <v>56.1</v>
@@ -8549,37 +8549,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M87">
-        <v>188.063469</v>
+        <v>190.2759804</v>
       </c>
       <c r="N87">
-        <v>-133.158469</v>
+        <v>-135.3709804</v>
       </c>
       <c r="O87">
-        <v>-42.61071008000001</v>
+        <v>-43.31871372800001</v>
       </c>
       <c r="P87">
-        <v>-90.54775892000001</v>
+        <v>-92.05226667200003</v>
       </c>
       <c r="Q87">
-        <v>-90.07775892000001</v>
+        <v>-91.58226667200003</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3060049183093588</v>
+        <v>0.3245909839028844</v>
       </c>
       <c r="T87">
-        <v>3.391342370899011</v>
+        <v>3.633581111677512</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.09342377918169741</v>
+        <v>0.09233745616795673</v>
       </c>
       <c r="W87">
-        <v>0.2137706728689558</v>
+        <v>0.2140268278355958</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2919493099428044</v>
+        <v>0.2885545505248648</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2295058096850162</v>
+        <v>0.2314058096850162</v>
       </c>
       <c r="C88">
-        <v>-560.0240145798836</v>
+        <v>-571.360329365199</v>
       </c>
       <c r="D88">
-        <v>190.8139854201166</v>
+        <v>188.8606706348009</v>
       </c>
       <c r="E88">
-        <v>463.8380000000001</v>
+        <v>473.221</v>
       </c>
       <c r="F88">
-        <v>806.9380000000001</v>
+        <v>816.321</v>
       </c>
       <c r="G88">
         <v>56.1</v>
@@ -8631,37 +8631,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M88">
-        <v>190.2759804</v>
+        <v>192.4884918</v>
       </c>
       <c r="N88">
-        <v>-135.3709804</v>
+        <v>-137.5834918</v>
       </c>
       <c r="O88">
-        <v>-43.31871372800001</v>
+        <v>-44.02671737600001</v>
       </c>
       <c r="P88">
-        <v>-92.05226667200003</v>
+        <v>-93.55677442400001</v>
       </c>
       <c r="Q88">
-        <v>-91.58226667200003</v>
+        <v>-93.08677442400001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3245909839028844</v>
+        <v>0.3460364442031063</v>
       </c>
       <c r="T88">
-        <v>3.633581111677512</v>
+        <v>3.91308735103732</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.09233745616795673</v>
+        <v>0.0912761060970607</v>
       </c>
       <c r="W88">
-        <v>0.2140268278355958</v>
+        <v>0.2142770941823131</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2885545505248648</v>
+        <v>0.2852378315533147</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2314058096850162</v>
+        <v>0.2333058096850162</v>
       </c>
       <c r="C89">
-        <v>-571.360329365199</v>
+        <v>-582.6570581974361</v>
       </c>
       <c r="D89">
-        <v>188.8606706348009</v>
+        <v>186.9469418025641</v>
       </c>
       <c r="E89">
-        <v>473.221</v>
+        <v>482.604</v>
       </c>
       <c r="F89">
-        <v>816.321</v>
+        <v>825.7040000000001</v>
       </c>
       <c r="G89">
         <v>56.1</v>
@@ -8713,37 +8713,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M89">
-        <v>192.4884918</v>
+        <v>194.7010032</v>
       </c>
       <c r="N89">
-        <v>-137.5834918</v>
+        <v>-139.7960032</v>
       </c>
       <c r="O89">
-        <v>-44.02671737600001</v>
+        <v>-44.73472102400001</v>
       </c>
       <c r="P89">
-        <v>-93.55677442400001</v>
+        <v>-95.06128217600002</v>
       </c>
       <c r="Q89">
-        <v>-93.08677442400001</v>
+        <v>-94.59128217600002</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3460364442031063</v>
+        <v>0.3710561478866986</v>
       </c>
       <c r="T89">
-        <v>3.91308735103732</v>
+        <v>4.239177963623765</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.0912761060970607</v>
+        <v>0.09023887761868499</v>
       </c>
       <c r="W89">
-        <v>0.2142770941823131</v>
+        <v>0.2145216726575141</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2852378315533147</v>
+        <v>0.2819964925583907</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2333058096850162</v>
+        <v>0.2352058096850162</v>
       </c>
       <c r="C90">
-        <v>-582.6570581974361</v>
+        <v>-593.9153923807727</v>
       </c>
       <c r="D90">
-        <v>186.9469418025641</v>
+        <v>185.0716076192274</v>
       </c>
       <c r="E90">
-        <v>482.604</v>
+        <v>491.9870000000001</v>
       </c>
       <c r="F90">
-        <v>825.7040000000001</v>
+        <v>835.0870000000001</v>
       </c>
       <c r="G90">
         <v>56.1</v>
@@ -8795,37 +8795,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M90">
-        <v>194.7010032</v>
+        <v>196.9135146</v>
       </c>
       <c r="N90">
-        <v>-139.7960032</v>
+        <v>-142.0085146</v>
       </c>
       <c r="O90">
-        <v>-44.73472102400001</v>
+        <v>-45.44272467200001</v>
       </c>
       <c r="P90">
-        <v>-95.06128217600002</v>
+        <v>-96.56578992800003</v>
       </c>
       <c r="Q90">
-        <v>-94.59128217600002</v>
+        <v>-96.09578992800003</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3710561478866986</v>
+        <v>0.4006248886036712</v>
       </c>
       <c r="T90">
-        <v>4.239177963623765</v>
+        <v>4.624557778498652</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.09023887761868499</v>
+        <v>0.08922495764544135</v>
       </c>
       <c r="W90">
-        <v>0.2145216726575141</v>
+        <v>0.2147607549872049</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2819964925583907</v>
+        <v>0.2788279926420042</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2352058096850162</v>
+        <v>0.2371058096850162</v>
       </c>
       <c r="C91">
-        <v>-593.9153923807727</v>
+        <v>-605.1364758924835</v>
       </c>
       <c r="D91">
-        <v>185.0716076192274</v>
+        <v>183.2335241075165</v>
       </c>
       <c r="E91">
-        <v>491.9870000000001</v>
+        <v>501.37</v>
       </c>
       <c r="F91">
-        <v>835.0870000000001</v>
+        <v>844.47</v>
       </c>
       <c r="G91">
         <v>56.1</v>
@@ -8877,37 +8877,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M91">
-        <v>196.9135146</v>
+        <v>199.126026</v>
       </c>
       <c r="N91">
-        <v>-142.0085146</v>
+        <v>-144.221026</v>
       </c>
       <c r="O91">
-        <v>-45.44272467200001</v>
+        <v>-46.15072832000001</v>
       </c>
       <c r="P91">
-        <v>-96.56578992800003</v>
+        <v>-98.07029768000001</v>
       </c>
       <c r="Q91">
-        <v>-96.09578992800003</v>
+        <v>-97.60029768000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4006248886036712</v>
+        <v>0.4361073774640383</v>
       </c>
       <c r="T91">
-        <v>4.624557778498652</v>
+        <v>5.087013556348517</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.08922495764544135</v>
+        <v>0.08823356922715866</v>
       </c>
       <c r="W91">
-        <v>0.2147607549872049</v>
+        <v>0.214994524376236</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2788279926420042</v>
+        <v>0.2757299038348708</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2371058096850162</v>
+        <v>0.2390058096850162</v>
       </c>
       <c r="C92">
-        <v>-605.1364758924835</v>
+        <v>-616.3214077100197</v>
       </c>
       <c r="D92">
-        <v>183.2335241075165</v>
+        <v>181.4315922899803</v>
       </c>
       <c r="E92">
-        <v>501.37</v>
+        <v>510.753</v>
       </c>
       <c r="F92">
-        <v>844.47</v>
+        <v>853.8530000000001</v>
       </c>
       <c r="G92">
         <v>56.1</v>
@@ -8959,37 +8959,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M92">
-        <v>199.126026</v>
+        <v>201.3385374</v>
       </c>
       <c r="N92">
-        <v>-144.221026</v>
+        <v>-146.4335374</v>
       </c>
       <c r="O92">
-        <v>-46.15072832000001</v>
+        <v>-46.85873196800001</v>
       </c>
       <c r="P92">
-        <v>-98.07029768000001</v>
+        <v>-99.57480543200002</v>
       </c>
       <c r="Q92">
-        <v>-97.60029768000001</v>
+        <v>-99.10480543200002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4361073774640383</v>
+        <v>0.4794748638489315</v>
       </c>
       <c r="T92">
-        <v>5.087013556348517</v>
+        <v>5.652237284831687</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.08823356922715866</v>
+        <v>0.08726396956532176</v>
       </c>
       <c r="W92">
-        <v>0.214994524376236</v>
+        <v>0.2152231559764971</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2757299038348708</v>
+        <v>0.2726999048916305</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2390058096850162</v>
+        <v>0.2409058096850162</v>
       </c>
       <c r="C93">
-        <v>-616.3214077100197</v>
+        <v>-627.4712440021194</v>
       </c>
       <c r="D93">
-        <v>181.4315922899803</v>
+        <v>179.6647559978807</v>
       </c>
       <c r="E93">
-        <v>510.753</v>
+        <v>520.1360000000001</v>
       </c>
       <c r="F93">
-        <v>853.8530000000001</v>
+        <v>863.2360000000001</v>
       </c>
       <c r="G93">
         <v>56.1</v>
@@ -9041,37 +9041,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M93">
-        <v>201.3385374</v>
+        <v>203.5510488</v>
       </c>
       <c r="N93">
-        <v>-146.4335374</v>
+        <v>-148.6460488</v>
       </c>
       <c r="O93">
-        <v>-46.85873196800001</v>
+        <v>-47.56673561600002</v>
       </c>
       <c r="P93">
-        <v>-99.57480543200002</v>
+        <v>-101.079313184</v>
       </c>
       <c r="Q93">
-        <v>-99.10480543200002</v>
+        <v>-100.609313184</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4794748638489315</v>
+        <v>0.533684221830048</v>
       </c>
       <c r="T93">
-        <v>5.652237284831687</v>
+        <v>6.35876694543565</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.08726396956532176</v>
+        <v>0.08631544815700304</v>
       </c>
       <c r="W93">
-        <v>0.2152231559764971</v>
+        <v>0.2154468173245787</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2726999048916305</v>
+        <v>0.2697357754906345</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2409058096850162</v>
+        <v>0.2428058096850162</v>
       </c>
       <c r="C94">
-        <v>-627.4712440021194</v>
+        <v>-638.5870001931261</v>
       </c>
       <c r="D94">
-        <v>179.6647559978807</v>
+        <v>177.9319998068741</v>
       </c>
       <c r="E94">
-        <v>520.1360000000001</v>
+        <v>529.5190000000001</v>
       </c>
       <c r="F94">
-        <v>863.2360000000001</v>
+        <v>872.6190000000001</v>
       </c>
       <c r="G94">
         <v>56.1</v>
@@ -9123,37 +9123,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M94">
-        <v>203.5510488</v>
+        <v>205.7635602</v>
       </c>
       <c r="N94">
-        <v>-148.6460488</v>
+        <v>-150.8585602</v>
       </c>
       <c r="O94">
-        <v>-47.56673561600002</v>
+        <v>-48.27473926400001</v>
       </c>
       <c r="P94">
-        <v>-101.079313184</v>
+        <v>-102.583820936</v>
       </c>
       <c r="Q94">
-        <v>-100.609313184</v>
+        <v>-102.113820936</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.533684221830048</v>
+        <v>0.6033819678057692</v>
       </c>
       <c r="T94">
-        <v>6.35876694543565</v>
+        <v>7.267162223355029</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.08631544815700304</v>
+        <v>0.08538732505854064</v>
       </c>
       <c r="W94">
-        <v>0.2154468173245787</v>
+        <v>0.2156656687511961</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2697357754906345</v>
+        <v>0.2668353908079395</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2428058096850162</v>
+        <v>0.2447058096850163</v>
       </c>
       <c r="C95">
-        <v>-638.5870001931261</v>
+        <v>-649.669652908994</v>
       </c>
       <c r="D95">
-        <v>177.9319998068741</v>
+        <v>176.2323470910061</v>
       </c>
       <c r="E95">
-        <v>529.5190000000001</v>
+        <v>538.902</v>
       </c>
       <c r="F95">
-        <v>872.6190000000001</v>
+        <v>882.0020000000001</v>
       </c>
       <c r="G95">
         <v>56.1</v>
@@ -9205,37 +9205,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M95">
-        <v>205.7635602</v>
+        <v>207.9760716</v>
       </c>
       <c r="N95">
-        <v>-150.8585602</v>
+        <v>-153.0710716</v>
       </c>
       <c r="O95">
-        <v>-48.27473926400001</v>
+        <v>-48.98274291200001</v>
       </c>
       <c r="P95">
-        <v>-102.583820936</v>
+        <v>-104.088328688</v>
       </c>
       <c r="Q95">
-        <v>-102.113820936</v>
+        <v>-103.618328688</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6033819678057692</v>
+        <v>0.6963122957733977</v>
       </c>
       <c r="T95">
-        <v>7.267162223355029</v>
+        <v>8.478355927247536</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.08538732505854064</v>
+        <v>0.08447894926004552</v>
       </c>
       <c r="W95">
-        <v>0.2156656687511961</v>
+        <v>0.2158798637644813</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2668353908079395</v>
+        <v>0.2639967164376423</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2447058096850163</v>
+        <v>0.2466058096850162</v>
       </c>
       <c r="C96">
-        <v>-649.669652908994</v>
+        <v>-660.7201418128168</v>
       </c>
       <c r="D96">
-        <v>176.2323470910061</v>
+        <v>174.5648581871833</v>
       </c>
       <c r="E96">
-        <v>538.902</v>
+        <v>548.2850000000001</v>
       </c>
       <c r="F96">
-        <v>882.0020000000001</v>
+        <v>891.3850000000001</v>
       </c>
       <c r="G96">
         <v>56.1</v>
@@ -9287,37 +9287,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M96">
-        <v>207.9760716</v>
+        <v>210.188583</v>
       </c>
       <c r="N96">
-        <v>-153.0710716</v>
+        <v>-155.283583</v>
       </c>
       <c r="O96">
-        <v>-48.98274291200001</v>
+        <v>-49.69074656000001</v>
       </c>
       <c r="P96">
-        <v>-104.088328688</v>
+        <v>-105.59283644</v>
       </c>
       <c r="Q96">
-        <v>-103.618328688</v>
+        <v>-105.12283644</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6963122957733977</v>
+        <v>0.8264147549280776</v>
       </c>
       <c r="T96">
-        <v>8.478355927247536</v>
+        <v>10.17402711269705</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.08447894926004552</v>
+        <v>0.08358969716257138</v>
       </c>
       <c r="W96">
-        <v>0.2158798637644813</v>
+        <v>0.2160895494090657</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2639967164376423</v>
+        <v>0.2612178036330356</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2466058096850162</v>
+        <v>0.2485058096850162</v>
       </c>
       <c r="C97">
-        <v>-660.7201418128168</v>
+        <v>-671.739371337126</v>
       </c>
       <c r="D97">
-        <v>174.5648581871833</v>
+        <v>172.9286286628741</v>
       </c>
       <c r="E97">
-        <v>548.2850000000001</v>
+        <v>557.6680000000001</v>
       </c>
       <c r="F97">
-        <v>891.3850000000001</v>
+        <v>900.7680000000001</v>
       </c>
       <c r="G97">
         <v>56.1</v>
@@ -9369,37 +9369,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M97">
-        <v>210.188583</v>
+        <v>212.4010944</v>
       </c>
       <c r="N97">
-        <v>-155.283583</v>
+        <v>-157.4960944</v>
       </c>
       <c r="O97">
-        <v>-49.69074656000001</v>
+        <v>-50.39875020800001</v>
       </c>
       <c r="P97">
-        <v>-105.59283644</v>
+        <v>-107.097344192</v>
       </c>
       <c r="Q97">
-        <v>-105.12283644</v>
+        <v>-106.627344192</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8264147549280776</v>
+        <v>1.021568443660097</v>
       </c>
       <c r="T97">
-        <v>10.17402711269705</v>
+        <v>12.71753389087132</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.08358969716257138</v>
+        <v>0.08271897115046124</v>
       </c>
       <c r="W97">
-        <v>0.2160895494090657</v>
+        <v>0.2162948666027213</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2612178036330356</v>
+        <v>0.2584967848451915</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2485058096850162</v>
+        <v>0.2504058096850162</v>
       </c>
       <c r="C98">
-        <v>-671.7393713371259</v>
+        <v>-682.7282123196733</v>
       </c>
       <c r="D98">
-        <v>172.9286286628741</v>
+        <v>171.3227876803268</v>
       </c>
       <c r="E98">
-        <v>557.668</v>
+        <v>567.051</v>
       </c>
       <c r="F98">
-        <v>900.768</v>
+        <v>910.1510000000001</v>
       </c>
       <c r="G98">
         <v>56.1</v>
@@ -9451,37 +9451,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M98">
-        <v>212.4010944</v>
+        <v>214.6136058</v>
       </c>
       <c r="N98">
-        <v>-157.4960944</v>
+        <v>-159.7086058</v>
       </c>
       <c r="O98">
-        <v>-50.398750208</v>
+        <v>-51.106753856</v>
       </c>
       <c r="P98">
-        <v>-107.097344192</v>
+        <v>-108.601851944</v>
       </c>
       <c r="Q98">
-        <v>-106.627344192</v>
+        <v>-108.131851944</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.021568443660095</v>
+        <v>1.346824591546793</v>
       </c>
       <c r="T98">
-        <v>12.71753389087128</v>
+        <v>16.95671185449504</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.08271897115046124</v>
+        <v>0.08186619825200289</v>
       </c>
       <c r="W98">
-        <v>0.2162948666027213</v>
+        <v>0.2164959504521777</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2584967848451915</v>
+        <v>0.255831869537509</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2504058096850162</v>
+        <v>0.2523058096850163</v>
       </c>
       <c r="C99">
-        <v>-682.7282123196733</v>
+        <v>-693.6875035489086</v>
       </c>
       <c r="D99">
-        <v>171.3227876803268</v>
+        <v>169.7464964510915</v>
       </c>
       <c r="E99">
-        <v>567.051</v>
+        <v>576.4340000000001</v>
       </c>
       <c r="F99">
-        <v>910.1510000000001</v>
+        <v>919.5340000000001</v>
       </c>
       <c r="G99">
         <v>56.1</v>
@@ -9533,37 +9533,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M99">
-        <v>214.6136058</v>
+        <v>216.8261172</v>
       </c>
       <c r="N99">
-        <v>-159.7086058</v>
+        <v>-161.9211172</v>
       </c>
       <c r="O99">
-        <v>-51.106753856</v>
+        <v>-51.81475750400001</v>
       </c>
       <c r="P99">
-        <v>-108.601851944</v>
+        <v>-110.106359696</v>
       </c>
       <c r="Q99">
-        <v>-108.131851944</v>
+        <v>-109.636359696</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.346824591546793</v>
+        <v>1.99733688732019</v>
       </c>
       <c r="T99">
-        <v>16.95671185449504</v>
+        <v>25.43506778174256</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.08186619825200289</v>
+        <v>0.08103082888208447</v>
       </c>
       <c r="W99">
-        <v>0.2164959504521777</v>
+        <v>0.2166929305496045</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.255831869537509</v>
+        <v>0.2532213402565141</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2523058096850163</v>
+        <v>0.2542058096850162</v>
       </c>
       <c r="C100">
-        <v>-693.6875035489086</v>
+        <v>-704.6180532249206</v>
       </c>
       <c r="D100">
-        <v>169.7464964510915</v>
+        <v>168.1989467750795</v>
       </c>
       <c r="E100">
-        <v>576.4340000000001</v>
+        <v>585.817</v>
       </c>
       <c r="F100">
-        <v>919.5340000000001</v>
+        <v>928.917</v>
       </c>
       <c r="G100">
         <v>56.1</v>
@@ -9615,37 +9615,37 @@
         <v>54.90499999999999</v>
       </c>
       <c r="M100">
-        <v>216.8261172</v>
+        <v>219.0386286</v>
       </c>
       <c r="N100">
-        <v>-161.9211172</v>
+        <v>-164.1336286</v>
       </c>
       <c r="O100">
-        <v>-51.81475750400001</v>
+        <v>-52.522761152</v>
       </c>
       <c r="P100">
-        <v>-110.106359696</v>
+        <v>-111.610867448</v>
       </c>
       <c r="Q100">
-        <v>-109.636359696</v>
+        <v>-111.140867448</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.99733688732019</v>
+        <v>3.948873774640379</v>
       </c>
       <c r="T100">
-        <v>25.43506778174256</v>
+        <v>50.87013556348512</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.08103082888208447</v>
+        <v>0.08021233566105333</v>
       </c>
       <c r="W100">
-        <v>0.2166929305496045</v>
+        <v>0.2168859312511236</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2532213402565141</v>
+        <v>0.2506635489407917</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2542058096850162</v>
-      </c>
-      <c r="C101">
-        <v>-704.6180532249206</v>
-      </c>
-      <c r="D101">
-        <v>168.1989467750795</v>
-      </c>
-      <c r="E101">
-        <v>585.817</v>
-      </c>
-      <c r="F101">
-        <v>928.917</v>
-      </c>
-      <c r="G101">
-        <v>56.1</v>
-      </c>
-      <c r="H101">
-        <v>595.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>55.37499999999999</v>
-      </c>
-      <c r="K101">
-        <v>0.47</v>
-      </c>
-      <c r="L101">
-        <v>54.90499999999999</v>
-      </c>
-      <c r="M101">
-        <v>219.0386286</v>
-      </c>
-      <c r="N101">
-        <v>-164.1336286</v>
-      </c>
-      <c r="O101">
-        <v>-52.522761152</v>
-      </c>
-      <c r="P101">
-        <v>-111.610867448</v>
-      </c>
-      <c r="Q101">
-        <v>-111.140867448</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.948873774640379</v>
-      </c>
-      <c r="T101">
-        <v>50.87013556348512</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.08021233566105333</v>
-      </c>
-      <c r="W101">
-        <v>0.2168859312511236</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2506635489407917</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
